--- a/IdentityHunt/Intel__SAMPLE_V1.xlsx
+++ b/IdentityHunt/Intel__SAMPLE_V1.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="403">
   <si>
     <t xml:space="preserve">query</t>
   </si>
@@ -186,28 +186,28 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">kevinrose</t>
+    <t xml:space="preserve">kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">3 - about.me</t>
   </si>
   <si>
-    <t xml:space="preserve">Kevin ROSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://about.me/kevinrose</t>
+    <t xml:space="preserve">kelvin ROSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://about.me/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">San Francisco, California, Meditator</t>
   </si>
   <si>
-    <t xml:space="preserve">Kevin</t>
+    <t xml:space="preserve">kelvin</t>
   </si>
   <si>
     <t xml:space="preserve">3 - cashapp</t>
   </si>
   <si>
-    <t xml:space="preserve">https://cash.app/$kevinrose</t>
+    <t xml:space="preserve">https://cash.app/$kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">US</t>
@@ -246,7 +246,7 @@
     <t xml:space="preserve">3 - instagram</t>
   </si>
   <si>
-    <t xml:space="preserve">https://instagram.com/kevinrose/</t>
+    <t xml:space="preserve">https://instagram.com/kelvinrose/</t>
   </si>
   <si>
     <t xml:space="preserve">124163</t>
@@ -255,7 +255,7 @@
     <t xml:space="preserve">3 - keybase</t>
   </si>
   <si>
-    <t xml:space="preserve">https://keybase.io/kevinrose</t>
+    <t xml:space="preserve">https://keybase.io/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">ROSE</t>
@@ -264,22 +264,10 @@
     <t xml:space="preserve">3 - paypal</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.paypal.com/paypalme/kevinrose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"givenName":"Kevin","familyName":"Rose","alternateFullName":"","displayName":"Kevin Rose","displayEmail":"","displayMobilePhone":"","displayAddress":"","profilePhotoUrl":"https:\u002F\u002Fpics.paypal.com\u002F00\u002Fp\u002FY2E1M2VjZjItYzUyYy00MzliLWJjYmUtYTA4YzVlZTBkYTY1\u002F$_58.jpg","primaryCurrencyCode":"USD","instagramUsername":"","facebookUrl":"","twitterHandle":"","website":""},"privacySettings":{"displayEmailEnabled":false,"displayMobilePhoneEnabled":false},"payerId":"S3CSYKHLL83E2","intent":"PERSONAL","shopId":"","paypalmeSlugName":"kevinrose","isProfileStatusActive":true,"networkIdentityStatus":"OPTED_IN","personalizationSettings":{"backgroundColor":"blue","transactionType":"PERSONAL","coverPhotoUrl":"https:\u002F\u002Fwww.paypalobjects.com\u002Fprofiles\u002Fcover\u002Fyellow.jpg","previewImage":"","welcomeNote":"","coverPhotoVerticalPan":"0","description":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3853471531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - spydialer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.spydialer.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UT?</t>
+    <t xml:space="preserve">https://www.paypal.com/paypalme/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"givenName":"kelvin","familyName":"Rose","alternateFullName":"","displayName":"kelvin Rose","displayEmail":"","displayMobilePhone":"","displayAddress":"","profilePhotoUrl":"https:\u002F\u002Fpics.paypal.com\u002F00\u002Fp\u002FY2E1M2VjZjItYzUyYy00MzliLWJjYmUtYTA4YzVlZTBkYTY1\u002F$_58.jpg","primaryCurrencyCode":"USD","instagramUsername":"","facebookUrl":"","twitterHandle":"","website":""},"privacySettings":{"displayEmailEnabled":false,"displayMobilePhoneEnabled":false},"payerId":"S3CSYKHLL83E2","intent":"PERSONAL","shopId":"","paypalmeSlugName":"kelvinrose","isProfileStatusActive":true,"networkIdentityStatus":"OPTED_IN","personalizationSettings":{"backgroundColor":"blue","transactionType":"PERSONAL","coverPhotoUrl":"https:\u002F\u002Fwww.paypalobjects.com\u002Fprofiles\u002Fcover\u002Fyellow.jpg","previewImage":"","welcomeNote":"","coverPhotoVerticalPan":"0","description":""</t>
   </si>
   <si>
     <t xml:space="preserve">4 - bitbucket</t>
@@ -297,19 +285,19 @@
     <t xml:space="preserve">4 - blogspot</t>
   </si>
   <si>
-    <t xml:space="preserve">https://kevinrose.blogspot.com</t>
+    <t xml:space="preserve">https://kelvinrose.blogspot.com</t>
   </si>
   <si>
     <t xml:space="preserve">4 - Facebook</t>
   </si>
   <si>
-    <t xml:space="preserve">https://facebook.com/kevinrose</t>
+    <t xml:space="preserve">https://facebook.com/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">4 - flickr</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.flickr.com/people/kevinrose</t>
+    <t xml:space="preserve">https://www.flickr.com/people/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">MR-JEFF</t>
@@ -324,76 +312,61 @@
     <t xml:space="preserve">4 - myspace</t>
   </si>
   <si>
-    <t xml:space="preserve">https://myspace.com/kevinrose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kevinwagner</t>
+    <t xml:space="preserve">https://myspace.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinwagner</t>
   </si>
   <si>
     <t xml:space="preserve">4 - pinterest</t>
   </si>
   <si>
-    <t xml:space="preserve">Kevin WAGNER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.pinterest.com/kevinwagner/</t>
+    <t xml:space="preserve">kelvin WAGNER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pinterest.com/kelvinwagner/</t>
   </si>
   <si>
     <t xml:space="preserve">4 - public</t>
   </si>
   <si>
-    <t xml:space="preserve">https://public.com/@kevinrose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 - whocalld</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://whocalld.com/+13853471531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">According to https://whocalld.com/+13853471531 3853471531 seems to be a mobile phone. The carrier for this number is New Cingular Wireless PCS in Murray, UT.</t>
+    <t xml:space="preserve">https://public.com/@kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">4 - wordpress</t>
   </si>
   <si>
-    <t xml:space="preserve">https://wordpress.org/support/users/kevinrose/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://kevinrose.wordspress.com</t>
+    <t xml:space="preserve">https://wordpress.org/support/users/kelvinrose/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://kelvinrose.wordspress.com</t>
   </si>
   <si>
     <t xml:space="preserve">4 - youtube</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.youtube.com/kevinrose</t>
+    <t xml:space="preserve">https://www.youtube.com/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">5 - bsky</t>
   </si>
   <si>
-    <t xml:space="preserve">https://bsky.app/profile/kevinrose.bsky.social</t>
+    <t xml:space="preserve">https://bsky.app/profile/kelvinrose.bsky.social</t>
   </si>
   <si>
     <t xml:space="preserve">5 - discus</t>
   </si>
   <si>
-    <t xml:space="preserve">http://disqus.com/kevinrose</t>
+    <t xml:space="preserve">http://disqus.com/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">5 - freelancer</t>
   </si>
   <si>
-    <t xml:space="preserve">Kevin W.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.freelancer.com/u/kevinwagner</t>
+    <t xml:space="preserve">kelvin W.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.freelancer.com/u/kelvinwagner</t>
   </si>
   <si>
     <t xml:space="preserve">KC3ELO</t>
@@ -423,13 +396,13 @@
     <t xml:space="preserve">5 - patreon</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.patreon.com/kevinrose/creators</t>
+    <t xml:space="preserve">https://www.patreon.com/kelvinrose/creators</t>
   </si>
   <si>
     <t xml:space="preserve">6 - reddit</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.reddit.com/user/kevinrose/</t>
+    <t xml:space="preserve">https://www.reddit.com/user/kelvinrose/</t>
   </si>
   <si>
     <t xml:space="preserve">2607:f0d0:1002:0051:0000:0000:0000:0004</t>
@@ -450,7 +423,7 @@
     <t xml:space="preserve">6 - slack</t>
   </si>
   <si>
-    <t xml:space="preserve">https://kevinrose.slack.com</t>
+    <t xml:space="preserve">https://kelvinrose.slack.com</t>
   </si>
   <si>
     <t xml:space="preserve">Misty0427</t>
@@ -474,7 +447,7 @@
     <t xml:space="preserve">7 - gravatar</t>
   </si>
   <si>
-    <t xml:space="preserve">http://en.gravatar.com/kevinrose</t>
+    <t xml:space="preserve">http://en.gravatar.com/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">https://2.gravatar.com/avatar/d0a79d0a107d87becfdeaa36ee662a74</t>
@@ -483,46 +456,422 @@
     <t xml:space="preserve">7 - instructables</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.instructables.com/member/kevinrose</t>
+    <t xml:space="preserve">https://www.instructables.com/member/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">7 - poshmark</t>
   </si>
   <si>
-    <t xml:space="preserve">https://poshmark.com/closet/kevinrose</t>
+    <t xml:space="preserve">https://poshmark.com/closet/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">7 - roblox</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.roblox.com/user.aspx?username=kevinrose</t>
+    <t xml:space="preserve">https://www.roblox.com/user.aspx?username=kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">7 - spotify</t>
   </si>
   <si>
-    <t xml:space="preserve">https://open.spotify.com/user/kevinrose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thekevinrose</t>
+    <t xml:space="preserve">https://open.spotify.com/user/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thekelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">7 - tinder</t>
   </si>
   <si>
-    <t xml:space="preserve">https://tinder.com/@thekevinrose</t>
+    <t xml:space="preserve">https://tinder.com/@thekelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">7 - whatnot</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.whatnot.com/user/kevinrose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 - familytree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.familytreenow.com/search/genealogy/results?phoneno=3853471531</t>
+    <t xml:space="preserve">https://www.whatnot.com/user/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - audiojungle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://audiojungle.net/user/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinRose's profile on AudioJungle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Success - 200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - bandcamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bandcamp.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose's collection | Bandcamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - bandlab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bandlab.com/api/v1.3/users/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - buzzfeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://buzzfeed.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose on BuzzFeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - carrd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://kelvinrose.carrd.co/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin R.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - chaturbate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://chaturbate.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaturbate - 100% Free Chat &amp; Webcams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - chess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.chess.com/member/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose - Chess Profile - Chess.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - couchsurfing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.couchsurfing.com/people/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin R. - Profile - Couchsurfing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - credly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.credly.com/users/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hub.docker.com/u/kelvinrose/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - dribbble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://dribbble.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dribbble - Discover the World’s Top Designers &amp; Creative Professionals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - erome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.erome.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinRose - Profile page - EroMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - genius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://genius.com/artists/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin Rose Lyrics, Songs, and Albums | Genius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - gitee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://gitee.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinRose (kelvinrose) - Gitee.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - gitlab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://gitlab.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin Rose · GitLab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - gravatar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose | Gravatar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - gumroad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.gumroad.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - hackaday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hackaday.io/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kevleeros's Profile | Hackaday.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - hackerone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hackerone.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HackerOne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - hive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hive.blog/@kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - hubpages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hubpages.com/@kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin Rose on HubPages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - huggingface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://huggingface.co/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose (kelvin Rose)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - ifttt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.ifttt.com/p/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose's Applets - IFTTT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - inkbunny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://inkbunny.net/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Members | Inkbunny, the Furry Art Community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - instapaper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.instapaper.com/p/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instapaper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - interpals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.interpals.net/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose (29), Jakarta, Indonesia - speaks Indonesian | InterPals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - kaggle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kaggle.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin Rose | Kaggle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - launchpad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://launchpad.net/~kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin Rose in Launchpad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - lichess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://lichess.org/@/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose : Activity • lichess.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - mastodon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mastodon.social/@kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin Rose (@kelvinrose@mastodon.social) - Mastodon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - memrise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.memrise.com/user/kelvinrose/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memrise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - mit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://scratch.mit.edu/users/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose on Scratch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - mixcloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.mixcloud.com/kelvinrose/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin Rose | Mixcloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - mojang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.mojang.com/users/profiles/minecraft/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - naver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://blog.naver.com/kelvinrose</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">kelvinrose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">님의블로그 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">네이버 블로그</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - periscope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.periscope.tv/kelvinrose/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - playerdb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://playerdb.co/api/player/minecraft/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - pokemonshowdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://pokemonshowdown.com/users/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose - Users - Pokémon Showdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - pornhub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://pornhub.com/users/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose's Profile - Pornhub.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - ppy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osu.ppy.sh/users/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinROSE‬ · player info‬ | ‭osu!‬</t>
   </si>
   <si>
     <t xml:space="preserve">Hmei7</t>
@@ -537,55 +886,208 @@
     <t xml:space="preserve">hasn't posted yet</t>
   </si>
   <si>
+    <t xml:space="preserve">8 - rumble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://rumble.com/user/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - sketchfab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://sketchfab.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose - Sketchfab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - soundcloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://soundcloud.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stream kelvin Rose music | Listen to songs, albums, playlists for free on SoundCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - speakerdeck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://speakerdeck.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose (@kelvinrose) on Speaker Deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - steemit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://steemit.com/@kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steemit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - tenor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tenor.com/users/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinROSE's GIFs on Tenor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - themeforest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://themeforest.net/user/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinRose's profile on ThemeForest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - themoviedb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.themoviedb.org/u/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose's Profile — The Movie Database (TMDB)</t>
+  </si>
+  <si>
     <t xml:space="preserve">8 - tiktok</t>
   </si>
   <si>
-    <t xml:space="preserve">https://tiktok.com/@kevinrose?</t>
+    <t xml:space="preserve">https://tiktok.com/@kelvinrose?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - tradingview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tradingview.com/u/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinRose — Trading Ideas and Scripts — TradingView</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tradingview.com/u/kelvinrose/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - tumblr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://kelvinrose.tumblr.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@kelvinrose on Tumblr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - ultimate-guitar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ultimate-guitar.com/u/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose | Ultimate-Guitar.Com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - unsplash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unsplash.com/@kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin Rose's Collections (@kelvinrose) | Unsplash Photo Community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - vk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vk.com/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VK.com | VK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - warriorforum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.warriorforum.com/members/kelvinrose.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinRose | Warrior Forum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - weebly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://kelvinrose.weebly.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin M. Rose - Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - wordnik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.wordnik.com/users/kelvinrose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welcome, kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">8 - wordpress</t>
   </si>
   <si>
-    <t xml:space="preserve">https://profiles.wordpress.org/kevinrose/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kevinrose@gmail.com</t>
+    <t xml:space="preserve">https://profiles.wordpress.org/kelvinrose/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 - youpic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youpic.com/photographer/kelvinrose/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvin Rose — YouPic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelvinrose@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">9 - calendar</t>
   </si>
   <si>
-    <t xml:space="preserve">https://calendar.google.com/calendar/u/0/embed?src=kevinrose@gmail.com&amp;pli=1</t>
+    <t xml:space="preserve">https://calendar.google.com/calendar/u/0/embed?src=kelvinrose@gmail.com&amp;pli=1</t>
   </si>
   <si>
     <t xml:space="preserve">9 - carrot2</t>
   </si>
   <si>
-    <t xml:space="preserve">https://search.carrot2.org/#/search/web/kevinrose@gmail.com/folders</t>
+    <t xml:space="preserve">https://search.carrot2.org/#/search/web/kelvinrose@gmail.com/folders</t>
   </si>
   <si>
     <t xml:space="preserve">9 - cyberbackground</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.cyberbackgroundchecks.com/email/kevinrose@gmail.com</t>
+    <t xml:space="preserve">https://www.cyberbackgroundchecks.com/email/kelvinrose@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">9 - epios</t>
   </si>
   <si>
-    <t xml:space="preserve">https://epieos.com/?q=kevinrose@gmail.com&amp;t=email</t>
+    <t xml:space="preserve">https://epieos.com/?q=kelvinrose@gmail.com&amp;t=email</t>
   </si>
   <si>
     <t xml:space="preserve">9 - garmin</t>
   </si>
   <si>
-    <t xml:space="preserve">https://connect.garmin.com/modern/profile/kevinrose</t>
+    <t xml:space="preserve">https://connect.garmin.com/modern/profile/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">9 - ghunt</t>
   </si>
   <si>
-    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\GHunt &amp;&amp; ghunt email kevinrose@gmail.com</t>
+    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\GHunt &amp;&amp; ghunt email kelvinrose@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">zazenergy</t>
@@ -603,70 +1105,64 @@
     <t xml:space="preserve">9 - instantusername</t>
   </si>
   <si>
-    <t xml:space="preserve">https://instantusername.com/?q=kevinrose</t>
+    <t xml:space="preserve">https://instantusername.com/?q=kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">9 - linkedin</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.linkedin.com/in/kevinrose</t>
+    <t xml:space="preserve">https://www.linkedin.com/in/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">9 - manual</t>
   </si>
   <si>
-    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\sherlock &amp;&amp; python sherlock kevinrose</t>
+    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\sherlock &amp;&amp; python sherlock kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">https://whatsmyname.app/</t>
   </si>
   <si>
-    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\WhatsMyName &amp;&amp; python web_accounts_list_checker.py -u kevinrose -of C:\Forensics\scripts\python\output_kevinrosetxt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\holehe &amp;&amp; holehe -NP --no-color --no-clear --only-used kevinrose@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\sherlock &amp;&amp; python sherlock kevinwagner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\WhatsMyName &amp;&amp; python web_accounts_list_checker.py -u kevinwagner -of C:\Forensics\scripts\python\output_kevinwagnertxt</t>
+    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\WhatsMyName &amp;&amp; python web_accounts_list_checker.py -u kelvinrose -of C:\Forensics\scripts\python\output_kelvinrosetxt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\holehe &amp;&amp; holehe -NP --no-color --no-clear --only-used kelvinrose@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\sherlock &amp;&amp; python sherlock kelvinwagner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cd C:\Forensics\scripts\python\git-repo\WhatsMyName &amp;&amp; python web_accounts_list_checker.py -u kelvinwagner -of C:\Forensics\scripts\python\output_kelvinwagnertxt</t>
   </si>
   <si>
     <t xml:space="preserve">9 - pinterest</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.pinterest.com/kevinrose/</t>
+    <t xml:space="preserve">https://www.pinterest.com/kelvinrose/</t>
   </si>
   <si>
     <t xml:space="preserve">9 - thatsthem</t>
   </si>
   <si>
-    <t xml:space="preserve">https://thatsthem.com/email/kevinrose@gmail.com</t>
+    <t xml:space="preserve">https://thatsthem.com/email/kelvinrose@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">9 - truepeoplesearch</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.truepeoplesearch.com/resultemail?email=kevinrose@gmail.com</t>
+    <t xml:space="preserve">https://www.truepeoplesearch.com/resultemail?email=kelvinrose@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">9 - truthsocial</t>
   </si>
   <si>
-    <t xml:space="preserve">https://truthsocial.com/@kevinrose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 - validnumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://validnumber.com/phone-number/3853471531/</t>
+    <t xml:space="preserve">https://truthsocial.com/@kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">9 - venmo</t>
   </si>
   <si>
-    <t xml:space="preserve">https://account.venmo.com/u/kevinrose</t>
+    <t xml:space="preserve">https://account.venmo.com/u/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">77.15.67.232</t>
@@ -678,12 +1174,6 @@
     <t xml:space="preserve">https://whatismyipaddress.com/ip/77.15.67.232</t>
   </si>
   <si>
-    <t xml:space="preserve">9 - whitepages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.whitepages.com/phone/1-3853471531</t>
-  </si>
-  <si>
     <t xml:space="preserve">9 - whois</t>
   </si>
   <si>
@@ -693,7 +1183,7 @@
     <t xml:space="preserve">9 - X</t>
   </si>
   <si>
-    <t xml:space="preserve">https://x.com/kevinrose</t>
+    <t xml:space="preserve">https://x.com/kelvinrose</t>
   </si>
   <si>
     <t xml:space="preserve">Color</t>
@@ -787,7 +1277,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -809,6 +1299,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -919,6 +1415,39 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFA500"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1094,7 +1623,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BB1048576"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="19" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="19" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="20"/>
@@ -1450,39 +1979,42 @@
     </row>
     <row r="9" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="F9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1490,13 +2022,13 @@
         <v>54</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>54</v>
@@ -1510,13 +2042,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>54</v>
@@ -1527,76 +2059,76 @@
     </row>
     <row r="13" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>96</v>
+        <v>54</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>100</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="T15" s="1" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>59</v>
@@ -1607,42 +2139,36 @@
         <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>111</v>
+      <c r="F18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1650,16 +2176,19 @@
         <v>54</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M19" s="1" t="s">
-        <v>114</v>
+      <c r="S19" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1667,36 +2196,30 @@
         <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>59</v>
@@ -1704,81 +2227,81 @@
     </row>
     <row r="22" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M23" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>126</v>
+      <c r="F24" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>54</v>
+        <v>129</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AX26" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1786,33 +2309,42 @@
         <v>54</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>54</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="F28" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AX28" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1820,42 +2352,30 @@
         <v>54</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="F29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q29" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>148</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1863,16 +2383,13 @@
         <v>54</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1880,10 +2397,10 @@
         <v>54</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>54</v>
@@ -1894,27 +2411,21 @@
         <v>54</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>54</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1922,442 +2433,4129 @@
         <v>54</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="0"/>
+      <c r="D36" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" s="0"/>
+      <c r="F36" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" s="0"/>
+      <c r="H36" s="0"/>
+      <c r="I36" s="0"/>
+      <c r="J36" s="0"/>
+      <c r="K36" s="0"/>
+      <c r="L36" s="0"/>
+      <c r="M36" s="0"/>
+      <c r="N36" s="0"/>
+      <c r="O36" s="0"/>
+      <c r="P36" s="0"/>
+      <c r="Q36" s="0"/>
+      <c r="R36" s="0"/>
+      <c r="S36" s="0"/>
+      <c r="T36" s="0"/>
+      <c r="U36" s="0"/>
+      <c r="V36" s="0"/>
+      <c r="W36" s="0"/>
+      <c r="X36" s="0"/>
+      <c r="Y36" s="0"/>
+      <c r="Z36" s="0"/>
+      <c r="AA36" s="0"/>
+      <c r="AB36" s="0"/>
+      <c r="AC36" s="0"/>
+      <c r="AD36" s="0"/>
+      <c r="AE36" s="0"/>
+      <c r="AF36" s="0"/>
+      <c r="AG36" s="0"/>
+      <c r="AH36" s="0"/>
+      <c r="AI36" s="0"/>
+      <c r="AJ36" s="0"/>
+      <c r="AK36" s="0"/>
+      <c r="AL36" s="0"/>
+      <c r="AM36" s="0"/>
+      <c r="AN36" s="0"/>
+      <c r="AO36" s="0"/>
+      <c r="AP36" s="0"/>
+      <c r="AQ36" s="0"/>
+      <c r="AR36" s="0"/>
+      <c r="AS36" s="0"/>
+      <c r="AT36" s="0"/>
+      <c r="AU36" s="0"/>
+      <c r="AV36" s="0" t="s">
         <v>158</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="AW36" s="0" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="AX36" s="0"/>
+      <c r="AY36" s="0"/>
+    </row>
+    <row r="37" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="0" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C37" s="0"/>
+      <c r="D37" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="E37" s="0"/>
+      <c r="F37" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G37" s="0"/>
+      <c r="H37" s="0"/>
+      <c r="I37" s="0"/>
+      <c r="J37" s="0"/>
+      <c r="K37" s="0"/>
+      <c r="L37" s="0"/>
+      <c r="M37" s="0"/>
+      <c r="N37" s="0"/>
+      <c r="O37" s="0"/>
+      <c r="P37" s="0"/>
+      <c r="Q37" s="0"/>
+      <c r="R37" s="0"/>
+      <c r="S37" s="0"/>
+      <c r="T37" s="0"/>
+      <c r="U37" s="0"/>
+      <c r="V37" s="0"/>
+      <c r="W37" s="0"/>
+      <c r="X37" s="0"/>
+      <c r="Y37" s="0"/>
+      <c r="Z37" s="0"/>
+      <c r="AA37" s="0"/>
+      <c r="AB37" s="0"/>
+      <c r="AC37" s="0"/>
+      <c r="AD37" s="0"/>
+      <c r="AE37" s="0"/>
+      <c r="AF37" s="0"/>
+      <c r="AG37" s="0"/>
+      <c r="AH37" s="0"/>
+      <c r="AI37" s="0"/>
+      <c r="AJ37" s="0"/>
+      <c r="AK37" s="0"/>
+      <c r="AL37" s="0"/>
+      <c r="AM37" s="0"/>
+      <c r="AN37" s="0"/>
+      <c r="AO37" s="0"/>
+      <c r="AP37" s="0"/>
+      <c r="AQ37" s="0"/>
+      <c r="AR37" s="0"/>
+      <c r="AS37" s="0"/>
+      <c r="AT37" s="0"/>
+      <c r="AU37" s="0"/>
+      <c r="AV37" s="0" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="1" t="s">
+      <c r="AW37" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX37" s="0"/>
+      <c r="AY37" s="0"/>
+    </row>
+    <row r="38" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="C38" s="0"/>
+      <c r="D38" s="0" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" s="1" t="s">
+      <c r="E38" s="0"/>
+      <c r="F38" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G38" s="0"/>
+      <c r="H38" s="0"/>
+      <c r="I38" s="0"/>
+      <c r="J38" s="0"/>
+      <c r="K38" s="0"/>
+      <c r="L38" s="0"/>
+      <c r="M38" s="0"/>
+      <c r="N38" s="0"/>
+      <c r="O38" s="0"/>
+      <c r="P38" s="0"/>
+      <c r="Q38" s="0"/>
+      <c r="R38" s="0"/>
+      <c r="S38" s="0"/>
+      <c r="T38" s="0"/>
+      <c r="U38" s="0"/>
+      <c r="V38" s="0"/>
+      <c r="W38" s="0"/>
+      <c r="X38" s="0"/>
+      <c r="Y38" s="0"/>
+      <c r="Z38" s="0"/>
+      <c r="AA38" s="0"/>
+      <c r="AB38" s="0"/>
+      <c r="AC38" s="0"/>
+      <c r="AD38" s="0"/>
+      <c r="AE38" s="0"/>
+      <c r="AF38" s="0"/>
+      <c r="AG38" s="0"/>
+      <c r="AH38" s="0"/>
+      <c r="AI38" s="0"/>
+      <c r="AJ38" s="0"/>
+      <c r="AK38" s="0"/>
+      <c r="AL38" s="0"/>
+      <c r="AM38" s="0"/>
+      <c r="AN38" s="0"/>
+      <c r="AO38" s="0"/>
+      <c r="AP38" s="0"/>
+      <c r="AQ38" s="0"/>
+      <c r="AR38" s="0"/>
+      <c r="AS38" s="0"/>
+      <c r="AT38" s="0"/>
+      <c r="AU38" s="0"/>
+      <c r="AV38" s="0"/>
+      <c r="AW38" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX38" s="0"/>
+      <c r="AY38" s="0"/>
+    </row>
+    <row r="39" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="C39" s="0"/>
+      <c r="D39" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="E39" s="0"/>
+      <c r="F39" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G39" s="0"/>
+      <c r="H39" s="0"/>
+      <c r="I39" s="0"/>
+      <c r="J39" s="0"/>
+      <c r="K39" s="0"/>
+      <c r="L39" s="0"/>
+      <c r="M39" s="0"/>
+      <c r="N39" s="0"/>
+      <c r="O39" s="0"/>
+      <c r="P39" s="0"/>
+      <c r="Q39" s="0"/>
+      <c r="R39" s="0"/>
+      <c r="S39" s="0"/>
+      <c r="T39" s="0"/>
+      <c r="U39" s="0"/>
+      <c r="V39" s="0"/>
+      <c r="W39" s="0"/>
+      <c r="X39" s="0"/>
+      <c r="Y39" s="0"/>
+      <c r="Z39" s="0"/>
+      <c r="AA39" s="0"/>
+      <c r="AB39" s="0"/>
+      <c r="AC39" s="0"/>
+      <c r="AD39" s="0"/>
+      <c r="AE39" s="0"/>
+      <c r="AF39" s="0"/>
+      <c r="AG39" s="0"/>
+      <c r="AH39" s="0"/>
+      <c r="AI39" s="0"/>
+      <c r="AJ39" s="0"/>
+      <c r="AK39" s="0"/>
+      <c r="AL39" s="0"/>
+      <c r="AM39" s="0"/>
+      <c r="AN39" s="0"/>
+      <c r="AO39" s="0"/>
+      <c r="AP39" s="0"/>
+      <c r="AQ39" s="0"/>
+      <c r="AR39" s="0"/>
+      <c r="AS39" s="0"/>
+      <c r="AT39" s="0"/>
+      <c r="AU39" s="0"/>
+      <c r="AV39" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="AW39" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX39" s="0"/>
+      <c r="AY39" s="0"/>
+    </row>
+    <row r="40" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="C40" s="0"/>
+      <c r="D40" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="M39" s="1" t="s">
+      <c r="E40" s="0"/>
+      <c r="F40" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G40" s="0"/>
+      <c r="H40" s="0"/>
+      <c r="I40" s="0"/>
+      <c r="J40" s="0"/>
+      <c r="K40" s="0"/>
+      <c r="L40" s="0"/>
+      <c r="M40" s="0"/>
+      <c r="N40" s="0"/>
+      <c r="O40" s="0"/>
+      <c r="P40" s="0"/>
+      <c r="Q40" s="0"/>
+      <c r="R40" s="0"/>
+      <c r="S40" s="0"/>
+      <c r="T40" s="0"/>
+      <c r="U40" s="0"/>
+      <c r="V40" s="0"/>
+      <c r="W40" s="0"/>
+      <c r="X40" s="0"/>
+      <c r="Y40" s="0"/>
+      <c r="Z40" s="0"/>
+      <c r="AA40" s="0"/>
+      <c r="AB40" s="0"/>
+      <c r="AC40" s="0"/>
+      <c r="AD40" s="0"/>
+      <c r="AE40" s="0"/>
+      <c r="AF40" s="0"/>
+      <c r="AG40" s="0"/>
+      <c r="AH40" s="0"/>
+      <c r="AI40" s="0"/>
+      <c r="AJ40" s="0"/>
+      <c r="AK40" s="0"/>
+      <c r="AL40" s="0"/>
+      <c r="AM40" s="0"/>
+      <c r="AN40" s="0"/>
+      <c r="AO40" s="0"/>
+      <c r="AP40" s="0"/>
+      <c r="AQ40" s="0"/>
+      <c r="AR40" s="0"/>
+      <c r="AS40" s="0"/>
+      <c r="AT40" s="0"/>
+      <c r="AU40" s="0"/>
+      <c r="AV40" s="0" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="1" t="s">
+      <c r="AW40" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX40" s="0"/>
+      <c r="AY40" s="0"/>
+    </row>
+    <row r="41" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="C41" s="0"/>
+      <c r="D41" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" s="1" t="s">
+      <c r="E41" s="0"/>
+      <c r="F41" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G41" s="0"/>
+      <c r="H41" s="0"/>
+      <c r="I41" s="0"/>
+      <c r="J41" s="0"/>
+      <c r="K41" s="0"/>
+      <c r="L41" s="0"/>
+      <c r="M41" s="0"/>
+      <c r="N41" s="0"/>
+      <c r="O41" s="0"/>
+      <c r="P41" s="0"/>
+      <c r="Q41" s="0"/>
+      <c r="R41" s="0"/>
+      <c r="S41" s="0"/>
+      <c r="T41" s="0"/>
+      <c r="U41" s="0"/>
+      <c r="V41" s="0"/>
+      <c r="W41" s="0"/>
+      <c r="X41" s="0"/>
+      <c r="Y41" s="0"/>
+      <c r="Z41" s="0"/>
+      <c r="AA41" s="0"/>
+      <c r="AB41" s="0"/>
+      <c r="AC41" s="0"/>
+      <c r="AD41" s="0"/>
+      <c r="AE41" s="0"/>
+      <c r="AF41" s="0"/>
+      <c r="AG41" s="0"/>
+      <c r="AH41" s="0"/>
+      <c r="AI41" s="0"/>
+      <c r="AJ41" s="0"/>
+      <c r="AK41" s="0"/>
+      <c r="AL41" s="0"/>
+      <c r="AM41" s="0"/>
+      <c r="AN41" s="0"/>
+      <c r="AO41" s="0"/>
+      <c r="AP41" s="0"/>
+      <c r="AQ41" s="0"/>
+      <c r="AR41" s="0"/>
+      <c r="AS41" s="0"/>
+      <c r="AT41" s="0"/>
+      <c r="AU41" s="0"/>
+      <c r="AV41" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="AW41" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX41" s="0"/>
+      <c r="AY41" s="0"/>
+    </row>
+    <row r="42" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="0" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
+      <c r="C42" s="0"/>
+      <c r="D42" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="E42" s="0"/>
+      <c r="F42" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G42" s="0"/>
+      <c r="H42" s="0"/>
+      <c r="I42" s="0"/>
+      <c r="J42" s="0"/>
+      <c r="K42" s="0"/>
+      <c r="L42" s="0"/>
+      <c r="M42" s="0"/>
+      <c r="N42" s="0"/>
+      <c r="O42" s="0"/>
+      <c r="P42" s="0"/>
+      <c r="Q42" s="0"/>
+      <c r="R42" s="0"/>
+      <c r="S42" s="0"/>
+      <c r="T42" s="0"/>
+      <c r="U42" s="0"/>
+      <c r="V42" s="0"/>
+      <c r="W42" s="0"/>
+      <c r="X42" s="0"/>
+      <c r="Y42" s="0"/>
+      <c r="Z42" s="0"/>
+      <c r="AA42" s="0"/>
+      <c r="AB42" s="0"/>
+      <c r="AC42" s="0"/>
+      <c r="AD42" s="0"/>
+      <c r="AE42" s="0"/>
+      <c r="AF42" s="0"/>
+      <c r="AG42" s="0"/>
+      <c r="AH42" s="0"/>
+      <c r="AI42" s="0"/>
+      <c r="AJ42" s="0"/>
+      <c r="AK42" s="0"/>
+      <c r="AL42" s="0"/>
+      <c r="AM42" s="0"/>
+      <c r="AN42" s="0"/>
+      <c r="AO42" s="0"/>
+      <c r="AP42" s="0"/>
+      <c r="AQ42" s="0"/>
+      <c r="AR42" s="0"/>
+      <c r="AS42" s="0"/>
+      <c r="AT42" s="0"/>
+      <c r="AU42" s="0"/>
+      <c r="AV42" s="0" t="s">
         <v>176</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="AW42" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX42" s="0"/>
+      <c r="AY42" s="0"/>
+    </row>
+    <row r="43" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B43" s="1" t="s">
+      <c r="C43" s="0"/>
+      <c r="D43" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="0"/>
+      <c r="F43" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G43" s="0"/>
+      <c r="H43" s="0"/>
+      <c r="I43" s="0"/>
+      <c r="J43" s="0"/>
+      <c r="K43" s="0"/>
+      <c r="L43" s="0"/>
+      <c r="M43" s="0"/>
+      <c r="N43" s="0"/>
+      <c r="O43" s="0"/>
+      <c r="P43" s="0"/>
+      <c r="Q43" s="0"/>
+      <c r="R43" s="0"/>
+      <c r="S43" s="0"/>
+      <c r="T43" s="0"/>
+      <c r="U43" s="0"/>
+      <c r="V43" s="0"/>
+      <c r="W43" s="0"/>
+      <c r="X43" s="0"/>
+      <c r="Y43" s="0"/>
+      <c r="Z43" s="0"/>
+      <c r="AA43" s="0"/>
+      <c r="AB43" s="0"/>
+      <c r="AC43" s="0"/>
+      <c r="AD43" s="0"/>
+      <c r="AE43" s="0"/>
+      <c r="AF43" s="0"/>
+      <c r="AG43" s="0"/>
+      <c r="AH43" s="0"/>
+      <c r="AI43" s="0"/>
+      <c r="AJ43" s="0"/>
+      <c r="AK43" s="0"/>
+      <c r="AL43" s="0"/>
+      <c r="AM43" s="0"/>
+      <c r="AN43" s="0"/>
+      <c r="AO43" s="0"/>
+      <c r="AP43" s="0"/>
+      <c r="AQ43" s="0"/>
+      <c r="AR43" s="0"/>
+      <c r="AS43" s="0"/>
+      <c r="AT43" s="0"/>
+      <c r="AU43" s="0"/>
+      <c r="AV43" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>175</v>
-      </c>
+      <c r="AW43" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX43" s="0"/>
+      <c r="AY43" s="0"/>
     </row>
     <row r="44" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B44" s="1" t="s">
+      <c r="A44" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="C44" s="0"/>
+      <c r="D44" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>175</v>
-      </c>
+      <c r="E44" s="0"/>
+      <c r="F44" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G44" s="0"/>
+      <c r="H44" s="0"/>
+      <c r="I44" s="0"/>
+      <c r="J44" s="0"/>
+      <c r="K44" s="0"/>
+      <c r="L44" s="0"/>
+      <c r="M44" s="0"/>
+      <c r="N44" s="0"/>
+      <c r="O44" s="0"/>
+      <c r="P44" s="0"/>
+      <c r="Q44" s="0"/>
+      <c r="R44" s="0"/>
+      <c r="S44" s="0"/>
+      <c r="T44" s="0"/>
+      <c r="U44" s="0"/>
+      <c r="V44" s="0"/>
+      <c r="W44" s="0"/>
+      <c r="X44" s="0"/>
+      <c r="Y44" s="0"/>
+      <c r="Z44" s="0"/>
+      <c r="AA44" s="0"/>
+      <c r="AB44" s="0"/>
+      <c r="AC44" s="0"/>
+      <c r="AD44" s="0"/>
+      <c r="AE44" s="0"/>
+      <c r="AF44" s="0"/>
+      <c r="AG44" s="0"/>
+      <c r="AH44" s="0"/>
+      <c r="AI44" s="0"/>
+      <c r="AJ44" s="0"/>
+      <c r="AK44" s="0"/>
+      <c r="AL44" s="0"/>
+      <c r="AM44" s="0"/>
+      <c r="AN44" s="0"/>
+      <c r="AO44" s="0"/>
+      <c r="AP44" s="0"/>
+      <c r="AQ44" s="0"/>
+      <c r="AR44" s="0"/>
+      <c r="AS44" s="0"/>
+      <c r="AT44" s="0"/>
+      <c r="AU44" s="0"/>
+      <c r="AV44" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="AW44" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX44" s="0"/>
+      <c r="AY44" s="0"/>
     </row>
     <row r="45" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="A45" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>175</v>
-      </c>
+      <c r="C45" s="0"/>
+      <c r="D45" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" s="0"/>
+      <c r="F45" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45" s="0"/>
+      <c r="H45" s="0"/>
+      <c r="I45" s="0"/>
+      <c r="J45" s="0"/>
+      <c r="K45" s="0"/>
+      <c r="L45" s="0"/>
+      <c r="M45" s="0"/>
+      <c r="N45" s="0"/>
+      <c r="O45" s="0"/>
+      <c r="P45" s="0"/>
+      <c r="Q45" s="0"/>
+      <c r="R45" s="0"/>
+      <c r="S45" s="0"/>
+      <c r="T45" s="0"/>
+      <c r="U45" s="0"/>
+      <c r="V45" s="0"/>
+      <c r="W45" s="0"/>
+      <c r="X45" s="0"/>
+      <c r="Y45" s="0"/>
+      <c r="Z45" s="0"/>
+      <c r="AA45" s="0"/>
+      <c r="AB45" s="0"/>
+      <c r="AC45" s="0"/>
+      <c r="AD45" s="0"/>
+      <c r="AE45" s="0"/>
+      <c r="AF45" s="0"/>
+      <c r="AG45" s="0"/>
+      <c r="AH45" s="0"/>
+      <c r="AI45" s="0"/>
+      <c r="AJ45" s="0"/>
+      <c r="AK45" s="0"/>
+      <c r="AL45" s="0"/>
+      <c r="AM45" s="0"/>
+      <c r="AN45" s="0"/>
+      <c r="AO45" s="0"/>
+      <c r="AP45" s="0"/>
+      <c r="AQ45" s="0"/>
+      <c r="AR45" s="0"/>
+      <c r="AS45" s="0"/>
+      <c r="AT45" s="0"/>
+      <c r="AU45" s="0"/>
+      <c r="AV45" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="AW45" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX45" s="0"/>
+      <c r="AY45" s="0"/>
     </row>
     <row r="46" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D46" s="1" t="s">
+      <c r="A46" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="C46" s="0"/>
+      <c r="D46" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="E46" s="0"/>
+      <c r="F46" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G46" s="0"/>
+      <c r="H46" s="0"/>
+      <c r="I46" s="0"/>
+      <c r="J46" s="0"/>
+      <c r="K46" s="0"/>
+      <c r="L46" s="0"/>
+      <c r="M46" s="0"/>
+      <c r="N46" s="0"/>
+      <c r="O46" s="0"/>
+      <c r="P46" s="0"/>
+      <c r="Q46" s="0"/>
+      <c r="R46" s="0"/>
+      <c r="S46" s="0"/>
+      <c r="T46" s="0"/>
+      <c r="U46" s="0"/>
+      <c r="V46" s="0"/>
+      <c r="W46" s="0"/>
+      <c r="X46" s="0"/>
+      <c r="Y46" s="0"/>
+      <c r="Z46" s="0"/>
+      <c r="AA46" s="0"/>
+      <c r="AB46" s="0"/>
+      <c r="AC46" s="0"/>
+      <c r="AD46" s="0"/>
+      <c r="AE46" s="0"/>
+      <c r="AF46" s="0"/>
+      <c r="AG46" s="0"/>
+      <c r="AH46" s="0"/>
+      <c r="AI46" s="0"/>
+      <c r="AJ46" s="0"/>
+      <c r="AK46" s="0"/>
+      <c r="AL46" s="0"/>
+      <c r="AM46" s="0"/>
+      <c r="AN46" s="0"/>
+      <c r="AO46" s="0"/>
+      <c r="AP46" s="0"/>
+      <c r="AQ46" s="0"/>
+      <c r="AR46" s="0"/>
+      <c r="AS46" s="0"/>
+      <c r="AT46" s="0"/>
+      <c r="AU46" s="0"/>
+      <c r="AV46" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="AW46" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX46" s="0"/>
+      <c r="AY46" s="0"/>
     </row>
     <row r="47" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>187</v>
-      </c>
+      <c r="A47" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" s="0"/>
+      <c r="D47" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="E47" s="0"/>
+      <c r="F47" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G47" s="0"/>
+      <c r="H47" s="0"/>
+      <c r="I47" s="0"/>
+      <c r="J47" s="0"/>
+      <c r="K47" s="0"/>
+      <c r="L47" s="0"/>
+      <c r="M47" s="0"/>
+      <c r="N47" s="0"/>
+      <c r="O47" s="0"/>
+      <c r="P47" s="0"/>
+      <c r="Q47" s="0"/>
+      <c r="R47" s="0"/>
+      <c r="S47" s="0"/>
+      <c r="T47" s="0"/>
+      <c r="U47" s="0"/>
+      <c r="V47" s="0"/>
+      <c r="W47" s="0"/>
+      <c r="X47" s="0"/>
+      <c r="Y47" s="0"/>
+      <c r="Z47" s="0"/>
+      <c r="AA47" s="0"/>
+      <c r="AB47" s="0"/>
+      <c r="AC47" s="0"/>
+      <c r="AD47" s="0"/>
+      <c r="AE47" s="0"/>
+      <c r="AF47" s="0"/>
+      <c r="AG47" s="0"/>
+      <c r="AH47" s="0"/>
+      <c r="AI47" s="0"/>
+      <c r="AJ47" s="0"/>
+      <c r="AK47" s="0"/>
+      <c r="AL47" s="0"/>
+      <c r="AM47" s="0"/>
+      <c r="AN47" s="0"/>
+      <c r="AO47" s="0"/>
+      <c r="AP47" s="0"/>
+      <c r="AQ47" s="0"/>
+      <c r="AR47" s="0"/>
+      <c r="AS47" s="0"/>
+      <c r="AT47" s="0"/>
+      <c r="AU47" s="0"/>
+      <c r="AV47" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="AW47" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX47" s="0"/>
+      <c r="AY47" s="0"/>
     </row>
     <row r="48" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="R48" s="1" t="s">
+      <c r="A48" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="0" t="s">
         <v>191</v>
       </c>
+      <c r="C48" s="0"/>
+      <c r="D48" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="E48" s="0"/>
+      <c r="F48" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G48" s="0"/>
+      <c r="H48" s="0"/>
+      <c r="I48" s="0"/>
+      <c r="J48" s="0"/>
+      <c r="K48" s="0"/>
+      <c r="L48" s="0"/>
+      <c r="M48" s="0"/>
+      <c r="N48" s="0"/>
+      <c r="O48" s="0"/>
+      <c r="P48" s="0"/>
+      <c r="Q48" s="0"/>
+      <c r="R48" s="0"/>
+      <c r="S48" s="0"/>
+      <c r="T48" s="0"/>
+      <c r="U48" s="0"/>
+      <c r="V48" s="0"/>
+      <c r="W48" s="0"/>
+      <c r="X48" s="0"/>
+      <c r="Y48" s="0"/>
+      <c r="Z48" s="0"/>
+      <c r="AA48" s="0"/>
+      <c r="AB48" s="0"/>
+      <c r="AC48" s="0"/>
+      <c r="AD48" s="0"/>
+      <c r="AE48" s="0"/>
+      <c r="AF48" s="0"/>
+      <c r="AG48" s="0"/>
+      <c r="AH48" s="0"/>
+      <c r="AI48" s="0"/>
+      <c r="AJ48" s="0"/>
+      <c r="AK48" s="0"/>
+      <c r="AL48" s="0"/>
+      <c r="AM48" s="0"/>
+      <c r="AN48" s="0"/>
+      <c r="AO48" s="0"/>
+      <c r="AP48" s="0"/>
+      <c r="AQ48" s="0"/>
+      <c r="AR48" s="0"/>
+      <c r="AS48" s="0"/>
+      <c r="AT48" s="0"/>
+      <c r="AU48" s="0"/>
+      <c r="AV48" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="AW48" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX48" s="0"/>
+      <c r="AY48" s="0"/>
     </row>
     <row r="49" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="A49" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="C49" s="0"/>
+      <c r="D49" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="E49" s="0"/>
+      <c r="F49" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G49" s="0"/>
+      <c r="H49" s="0"/>
+      <c r="I49" s="0"/>
+      <c r="J49" s="0"/>
+      <c r="K49" s="0"/>
+      <c r="L49" s="0"/>
+      <c r="M49" s="0"/>
+      <c r="N49" s="0"/>
+      <c r="O49" s="0"/>
+      <c r="P49" s="0"/>
+      <c r="Q49" s="0"/>
+      <c r="R49" s="0"/>
+      <c r="S49" s="0"/>
+      <c r="T49" s="0"/>
+      <c r="U49" s="0"/>
+      <c r="V49" s="0"/>
+      <c r="W49" s="0"/>
+      <c r="X49" s="0"/>
+      <c r="Y49" s="0"/>
+      <c r="Z49" s="0"/>
+      <c r="AA49" s="0"/>
+      <c r="AB49" s="0"/>
+      <c r="AC49" s="0"/>
+      <c r="AD49" s="0"/>
+      <c r="AE49" s="0"/>
+      <c r="AF49" s="0"/>
+      <c r="AG49" s="0"/>
+      <c r="AH49" s="0"/>
+      <c r="AI49" s="0"/>
+      <c r="AJ49" s="0"/>
+      <c r="AK49" s="0"/>
+      <c r="AL49" s="0"/>
+      <c r="AM49" s="0"/>
+      <c r="AN49" s="0"/>
+      <c r="AO49" s="0"/>
+      <c r="AP49" s="0"/>
+      <c r="AQ49" s="0"/>
+      <c r="AR49" s="0"/>
+      <c r="AS49" s="0"/>
+      <c r="AT49" s="0"/>
+      <c r="AU49" s="0"/>
+      <c r="AV49" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="AW49" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX49" s="0"/>
+      <c r="AY49" s="0"/>
     </row>
     <row r="50" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="A50" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="C50" s="0"/>
+      <c r="D50" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="E50" s="0"/>
+      <c r="F50" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G50" s="0"/>
+      <c r="H50" s="0"/>
+      <c r="I50" s="0"/>
+      <c r="J50" s="0"/>
+      <c r="K50" s="0"/>
+      <c r="L50" s="0"/>
+      <c r="M50" s="0"/>
+      <c r="N50" s="0"/>
+      <c r="O50" s="0"/>
+      <c r="P50" s="0"/>
+      <c r="Q50" s="0"/>
+      <c r="R50" s="0"/>
+      <c r="S50" s="0"/>
+      <c r="T50" s="0"/>
+      <c r="U50" s="0"/>
+      <c r="V50" s="0"/>
+      <c r="W50" s="0"/>
+      <c r="X50" s="0"/>
+      <c r="Y50" s="0"/>
+      <c r="Z50" s="0"/>
+      <c r="AA50" s="0"/>
+      <c r="AB50" s="0"/>
+      <c r="AC50" s="0"/>
+      <c r="AD50" s="0"/>
+      <c r="AE50" s="0"/>
+      <c r="AF50" s="0"/>
+      <c r="AG50" s="0"/>
+      <c r="AH50" s="0"/>
+      <c r="AI50" s="0"/>
+      <c r="AJ50" s="0"/>
+      <c r="AK50" s="0"/>
+      <c r="AL50" s="0"/>
+      <c r="AM50" s="0"/>
+      <c r="AN50" s="0"/>
+      <c r="AO50" s="0"/>
+      <c r="AP50" s="0"/>
+      <c r="AQ50" s="0"/>
+      <c r="AR50" s="0"/>
+      <c r="AS50" s="0"/>
+      <c r="AT50" s="0"/>
+      <c r="AU50" s="0"/>
+      <c r="AV50" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="AW50" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX50" s="0"/>
+      <c r="AY50" s="0"/>
     </row>
     <row r="51" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>197</v>
-      </c>
+      <c r="A51" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" s="0"/>
+      <c r="D51" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="E51" s="0"/>
+      <c r="F51" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G51" s="0"/>
+      <c r="H51" s="0"/>
+      <c r="I51" s="0"/>
+      <c r="J51" s="0"/>
+      <c r="K51" s="0"/>
+      <c r="L51" s="0"/>
+      <c r="M51" s="0"/>
+      <c r="N51" s="0"/>
+      <c r="O51" s="0"/>
+      <c r="P51" s="0"/>
+      <c r="Q51" s="0"/>
+      <c r="R51" s="0"/>
+      <c r="S51" s="0"/>
+      <c r="T51" s="0"/>
+      <c r="U51" s="0"/>
+      <c r="V51" s="0"/>
+      <c r="W51" s="0"/>
+      <c r="X51" s="0"/>
+      <c r="Y51" s="0"/>
+      <c r="Z51" s="0"/>
+      <c r="AA51" s="0"/>
+      <c r="AB51" s="0"/>
+      <c r="AC51" s="0"/>
+      <c r="AD51" s="0"/>
+      <c r="AE51" s="0"/>
+      <c r="AF51" s="0"/>
+      <c r="AG51" s="0"/>
+      <c r="AH51" s="0"/>
+      <c r="AI51" s="0"/>
+      <c r="AJ51" s="0"/>
+      <c r="AK51" s="0"/>
+      <c r="AL51" s="0"/>
+      <c r="AM51" s="0"/>
+      <c r="AN51" s="0"/>
+      <c r="AO51" s="0"/>
+      <c r="AP51" s="0"/>
+      <c r="AQ51" s="0"/>
+      <c r="AR51" s="0"/>
+      <c r="AS51" s="0"/>
+      <c r="AT51" s="0"/>
+      <c r="AU51" s="0"/>
+      <c r="AV51" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="AW51" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX51" s="0"/>
+      <c r="AY51" s="0"/>
     </row>
     <row r="52" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>199</v>
-      </c>
+      <c r="A52" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="C52" s="0"/>
+      <c r="D52" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="E52" s="0"/>
+      <c r="F52" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G52" s="0"/>
+      <c r="H52" s="0"/>
+      <c r="I52" s="0"/>
+      <c r="J52" s="0"/>
+      <c r="K52" s="0"/>
+      <c r="L52" s="0"/>
+      <c r="M52" s="0"/>
+      <c r="N52" s="0"/>
+      <c r="O52" s="0"/>
+      <c r="P52" s="0"/>
+      <c r="Q52" s="0"/>
+      <c r="R52" s="0"/>
+      <c r="S52" s="0"/>
+      <c r="T52" s="0"/>
+      <c r="U52" s="0"/>
+      <c r="V52" s="0"/>
+      <c r="W52" s="0"/>
+      <c r="X52" s="0"/>
+      <c r="Y52" s="0"/>
+      <c r="Z52" s="0"/>
+      <c r="AA52" s="0"/>
+      <c r="AB52" s="0"/>
+      <c r="AC52" s="0"/>
+      <c r="AD52" s="0"/>
+      <c r="AE52" s="0"/>
+      <c r="AF52" s="0"/>
+      <c r="AG52" s="0"/>
+      <c r="AH52" s="0"/>
+      <c r="AI52" s="0"/>
+      <c r="AJ52" s="0"/>
+      <c r="AK52" s="0"/>
+      <c r="AL52" s="0"/>
+      <c r="AM52" s="0"/>
+      <c r="AN52" s="0"/>
+      <c r="AO52" s="0"/>
+      <c r="AP52" s="0"/>
+      <c r="AQ52" s="0"/>
+      <c r="AR52" s="0"/>
+      <c r="AS52" s="0"/>
+      <c r="AT52" s="0"/>
+      <c r="AU52" s="0"/>
+      <c r="AV52" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="AW52" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX52" s="0"/>
+      <c r="AY52" s="0"/>
     </row>
     <row r="53" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>200</v>
-      </c>
+      <c r="A53" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="C53" s="0"/>
+      <c r="D53" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="E53" s="0"/>
+      <c r="F53" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G53" s="0"/>
+      <c r="H53" s="0"/>
+      <c r="I53" s="0"/>
+      <c r="J53" s="0"/>
+      <c r="K53" s="0"/>
+      <c r="L53" s="0"/>
+      <c r="M53" s="0"/>
+      <c r="N53" s="0"/>
+      <c r="O53" s="0"/>
+      <c r="P53" s="0"/>
+      <c r="Q53" s="0"/>
+      <c r="R53" s="0"/>
+      <c r="S53" s="0"/>
+      <c r="T53" s="0"/>
+      <c r="U53" s="0"/>
+      <c r="V53" s="0"/>
+      <c r="W53" s="0"/>
+      <c r="X53" s="0"/>
+      <c r="Y53" s="0"/>
+      <c r="Z53" s="0"/>
+      <c r="AA53" s="0"/>
+      <c r="AB53" s="0"/>
+      <c r="AC53" s="0"/>
+      <c r="AD53" s="0"/>
+      <c r="AE53" s="0"/>
+      <c r="AF53" s="0"/>
+      <c r="AG53" s="0"/>
+      <c r="AH53" s="0"/>
+      <c r="AI53" s="0"/>
+      <c r="AJ53" s="0"/>
+      <c r="AK53" s="0"/>
+      <c r="AL53" s="0"/>
+      <c r="AM53" s="0"/>
+      <c r="AN53" s="0"/>
+      <c r="AO53" s="0"/>
+      <c r="AP53" s="0"/>
+      <c r="AQ53" s="0"/>
+      <c r="AR53" s="0"/>
+      <c r="AS53" s="0"/>
+      <c r="AT53" s="0"/>
+      <c r="AU53" s="0"/>
+      <c r="AV53" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="AW53" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX53" s="0"/>
+      <c r="AY53" s="0"/>
     </row>
     <row r="54" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>201</v>
-      </c>
+      <c r="A54" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="C54" s="0"/>
+      <c r="D54" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="E54" s="0"/>
+      <c r="F54" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G54" s="0"/>
+      <c r="H54" s="0"/>
+      <c r="I54" s="0"/>
+      <c r="J54" s="0"/>
+      <c r="K54" s="0"/>
+      <c r="L54" s="0"/>
+      <c r="M54" s="0"/>
+      <c r="N54" s="0"/>
+      <c r="O54" s="0"/>
+      <c r="P54" s="0"/>
+      <c r="Q54" s="0"/>
+      <c r="R54" s="0"/>
+      <c r="S54" s="0"/>
+      <c r="T54" s="0"/>
+      <c r="U54" s="0"/>
+      <c r="V54" s="0"/>
+      <c r="W54" s="0"/>
+      <c r="X54" s="0"/>
+      <c r="Y54" s="0"/>
+      <c r="Z54" s="0"/>
+      <c r="AA54" s="0"/>
+      <c r="AB54" s="0"/>
+      <c r="AC54" s="0"/>
+      <c r="AD54" s="0"/>
+      <c r="AE54" s="0"/>
+      <c r="AF54" s="0"/>
+      <c r="AG54" s="0"/>
+      <c r="AH54" s="0"/>
+      <c r="AI54" s="0"/>
+      <c r="AJ54" s="0"/>
+      <c r="AK54" s="0"/>
+      <c r="AL54" s="0"/>
+      <c r="AM54" s="0"/>
+      <c r="AN54" s="0"/>
+      <c r="AO54" s="0"/>
+      <c r="AP54" s="0"/>
+      <c r="AQ54" s="0"/>
+      <c r="AR54" s="0"/>
+      <c r="AS54" s="0"/>
+      <c r="AT54" s="0"/>
+      <c r="AU54" s="0"/>
+      <c r="AV54" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="AW54" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX54" s="0"/>
+      <c r="AY54" s="0"/>
     </row>
     <row r="55" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>202</v>
-      </c>
+      <c r="A55" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="C55" s="0"/>
+      <c r="D55" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="E55" s="0"/>
+      <c r="F55" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G55" s="0"/>
+      <c r="H55" s="0"/>
+      <c r="I55" s="0"/>
+      <c r="J55" s="0"/>
+      <c r="K55" s="0"/>
+      <c r="L55" s="0"/>
+      <c r="M55" s="0"/>
+      <c r="N55" s="0"/>
+      <c r="O55" s="0"/>
+      <c r="P55" s="0"/>
+      <c r="Q55" s="0"/>
+      <c r="R55" s="0"/>
+      <c r="S55" s="0"/>
+      <c r="T55" s="0"/>
+      <c r="U55" s="0"/>
+      <c r="V55" s="0"/>
+      <c r="W55" s="0"/>
+      <c r="X55" s="0"/>
+      <c r="Y55" s="0"/>
+      <c r="Z55" s="0"/>
+      <c r="AA55" s="0"/>
+      <c r="AB55" s="0"/>
+      <c r="AC55" s="0"/>
+      <c r="AD55" s="0"/>
+      <c r="AE55" s="0"/>
+      <c r="AF55" s="0"/>
+      <c r="AG55" s="0"/>
+      <c r="AH55" s="0"/>
+      <c r="AI55" s="0"/>
+      <c r="AJ55" s="0"/>
+      <c r="AK55" s="0"/>
+      <c r="AL55" s="0"/>
+      <c r="AM55" s="0"/>
+      <c r="AN55" s="0"/>
+      <c r="AO55" s="0"/>
+      <c r="AP55" s="0"/>
+      <c r="AQ55" s="0"/>
+      <c r="AR55" s="0"/>
+      <c r="AS55" s="0"/>
+      <c r="AT55" s="0"/>
+      <c r="AU55" s="0"/>
+      <c r="AV55" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="AW55" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX55" s="0"/>
+      <c r="AY55" s="0"/>
     </row>
     <row r="56" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="A56" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="0"/>
+      <c r="D56" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E56" s="0"/>
+      <c r="F56" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G56" s="0"/>
+      <c r="H56" s="0"/>
+      <c r="I56" s="0"/>
+      <c r="J56" s="0"/>
+      <c r="K56" s="0"/>
+      <c r="L56" s="0"/>
+      <c r="M56" s="0"/>
+      <c r="N56" s="0"/>
+      <c r="O56" s="0"/>
+      <c r="P56" s="0"/>
+      <c r="Q56" s="0"/>
+      <c r="R56" s="0"/>
+      <c r="S56" s="0"/>
+      <c r="T56" s="0"/>
+      <c r="U56" s="0"/>
+      <c r="V56" s="0"/>
+      <c r="W56" s="0"/>
+      <c r="X56" s="0"/>
+      <c r="Y56" s="0"/>
+      <c r="Z56" s="0"/>
+      <c r="AA56" s="0"/>
+      <c r="AB56" s="0"/>
+      <c r="AC56" s="0"/>
+      <c r="AD56" s="0"/>
+      <c r="AE56" s="0"/>
+      <c r="AF56" s="0"/>
+      <c r="AG56" s="0"/>
+      <c r="AH56" s="0"/>
+      <c r="AI56" s="0"/>
+      <c r="AJ56" s="0"/>
+      <c r="AK56" s="0"/>
+      <c r="AL56" s="0"/>
+      <c r="AM56" s="0"/>
+      <c r="AN56" s="0"/>
+      <c r="AO56" s="0"/>
+      <c r="AP56" s="0"/>
+      <c r="AQ56" s="0"/>
+      <c r="AR56" s="0"/>
+      <c r="AS56" s="0"/>
+      <c r="AT56" s="0"/>
+      <c r="AU56" s="0"/>
+      <c r="AV56" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="AW56" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX56" s="0"/>
+      <c r="AY56" s="0"/>
     </row>
     <row r="57" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>175</v>
-      </c>
+      <c r="A57" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="C57" s="0"/>
+      <c r="D57" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="E57" s="0"/>
+      <c r="F57" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G57" s="0"/>
+      <c r="H57" s="0"/>
+      <c r="I57" s="0"/>
+      <c r="J57" s="0"/>
+      <c r="K57" s="0"/>
+      <c r="L57" s="0"/>
+      <c r="M57" s="0"/>
+      <c r="N57" s="0"/>
+      <c r="O57" s="0"/>
+      <c r="P57" s="0"/>
+      <c r="Q57" s="0"/>
+      <c r="R57" s="0"/>
+      <c r="S57" s="0"/>
+      <c r="T57" s="0"/>
+      <c r="U57" s="0"/>
+      <c r="V57" s="0"/>
+      <c r="W57" s="0"/>
+      <c r="X57" s="0"/>
+      <c r="Y57" s="0"/>
+      <c r="Z57" s="0"/>
+      <c r="AA57" s="0"/>
+      <c r="AB57" s="0"/>
+      <c r="AC57" s="0"/>
+      <c r="AD57" s="0"/>
+      <c r="AE57" s="0"/>
+      <c r="AF57" s="0"/>
+      <c r="AG57" s="0"/>
+      <c r="AH57" s="0"/>
+      <c r="AI57" s="0"/>
+      <c r="AJ57" s="0"/>
+      <c r="AK57" s="0"/>
+      <c r="AL57" s="0"/>
+      <c r="AM57" s="0"/>
+      <c r="AN57" s="0"/>
+      <c r="AO57" s="0"/>
+      <c r="AP57" s="0"/>
+      <c r="AQ57" s="0"/>
+      <c r="AR57" s="0"/>
+      <c r="AS57" s="0"/>
+      <c r="AT57" s="0"/>
+      <c r="AU57" s="0"/>
+      <c r="AV57" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW57" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX57" s="0"/>
+      <c r="AY57" s="0"/>
     </row>
     <row r="58" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>175</v>
-      </c>
+      <c r="A58" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58" s="0"/>
+      <c r="D58" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="E58" s="0"/>
+      <c r="F58" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G58" s="0"/>
+      <c r="H58" s="0"/>
+      <c r="I58" s="0"/>
+      <c r="J58" s="0"/>
+      <c r="K58" s="0"/>
+      <c r="L58" s="0"/>
+      <c r="M58" s="0"/>
+      <c r="N58" s="0"/>
+      <c r="O58" s="0"/>
+      <c r="P58" s="0"/>
+      <c r="Q58" s="0"/>
+      <c r="R58" s="0"/>
+      <c r="S58" s="0"/>
+      <c r="T58" s="0"/>
+      <c r="U58" s="0"/>
+      <c r="V58" s="0"/>
+      <c r="W58" s="0"/>
+      <c r="X58" s="0"/>
+      <c r="Y58" s="0"/>
+      <c r="Z58" s="0"/>
+      <c r="AA58" s="0"/>
+      <c r="AB58" s="0"/>
+      <c r="AC58" s="0"/>
+      <c r="AD58" s="0"/>
+      <c r="AE58" s="0"/>
+      <c r="AF58" s="0"/>
+      <c r="AG58" s="0"/>
+      <c r="AH58" s="0"/>
+      <c r="AI58" s="0"/>
+      <c r="AJ58" s="0"/>
+      <c r="AK58" s="0"/>
+      <c r="AL58" s="0"/>
+      <c r="AM58" s="0"/>
+      <c r="AN58" s="0"/>
+      <c r="AO58" s="0"/>
+      <c r="AP58" s="0"/>
+      <c r="AQ58" s="0"/>
+      <c r="AR58" s="0"/>
+      <c r="AS58" s="0"/>
+      <c r="AT58" s="0"/>
+      <c r="AU58" s="0"/>
+      <c r="AV58" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="AW58" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX58" s="0"/>
+      <c r="AY58" s="0"/>
     </row>
     <row r="59" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="A59" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="C59" s="0"/>
+      <c r="D59" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="E59" s="0"/>
+      <c r="F59" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G59" s="0"/>
+      <c r="H59" s="0"/>
+      <c r="I59" s="0"/>
+      <c r="J59" s="0"/>
+      <c r="K59" s="0"/>
+      <c r="L59" s="0"/>
+      <c r="M59" s="0"/>
+      <c r="N59" s="0"/>
+      <c r="O59" s="0"/>
+      <c r="P59" s="0"/>
+      <c r="Q59" s="0"/>
+      <c r="R59" s="0"/>
+      <c r="S59" s="0"/>
+      <c r="T59" s="0"/>
+      <c r="U59" s="0"/>
+      <c r="V59" s="0"/>
+      <c r="W59" s="0"/>
+      <c r="X59" s="0"/>
+      <c r="Y59" s="0"/>
+      <c r="Z59" s="0"/>
+      <c r="AA59" s="0"/>
+      <c r="AB59" s="0"/>
+      <c r="AC59" s="0"/>
+      <c r="AD59" s="0"/>
+      <c r="AE59" s="0"/>
+      <c r="AF59" s="0"/>
+      <c r="AG59" s="0"/>
+      <c r="AH59" s="0"/>
+      <c r="AI59" s="0"/>
+      <c r="AJ59" s="0"/>
+      <c r="AK59" s="0"/>
+      <c r="AL59" s="0"/>
+      <c r="AM59" s="0"/>
+      <c r="AN59" s="0"/>
+      <c r="AO59" s="0"/>
+      <c r="AP59" s="0"/>
+      <c r="AQ59" s="0"/>
+      <c r="AR59" s="0"/>
+      <c r="AS59" s="0"/>
+      <c r="AT59" s="0"/>
+      <c r="AU59" s="0"/>
+      <c r="AV59" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="AW59" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX59" s="0"/>
+      <c r="AY59" s="0"/>
     </row>
     <row r="60" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>110</v>
-      </c>
+      <c r="A60" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="C60" s="0"/>
+      <c r="D60" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="E60" s="0"/>
+      <c r="F60" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G60" s="0"/>
+      <c r="H60" s="0"/>
+      <c r="I60" s="0"/>
+      <c r="J60" s="0"/>
+      <c r="K60" s="0"/>
+      <c r="L60" s="0"/>
+      <c r="M60" s="0"/>
+      <c r="N60" s="0"/>
+      <c r="O60" s="0"/>
+      <c r="P60" s="0"/>
+      <c r="Q60" s="0"/>
+      <c r="R60" s="0"/>
+      <c r="S60" s="0"/>
+      <c r="T60" s="0"/>
+      <c r="U60" s="0"/>
+      <c r="V60" s="0"/>
+      <c r="W60" s="0"/>
+      <c r="X60" s="0"/>
+      <c r="Y60" s="0"/>
+      <c r="Z60" s="0"/>
+      <c r="AA60" s="0"/>
+      <c r="AB60" s="0"/>
+      <c r="AC60" s="0"/>
+      <c r="AD60" s="0"/>
+      <c r="AE60" s="0"/>
+      <c r="AF60" s="0"/>
+      <c r="AG60" s="0"/>
+      <c r="AH60" s="0"/>
+      <c r="AI60" s="0"/>
+      <c r="AJ60" s="0"/>
+      <c r="AK60" s="0"/>
+      <c r="AL60" s="0"/>
+      <c r="AM60" s="0"/>
+      <c r="AN60" s="0"/>
+      <c r="AO60" s="0"/>
+      <c r="AP60" s="0"/>
+      <c r="AQ60" s="0"/>
+      <c r="AR60" s="0"/>
+      <c r="AS60" s="0"/>
+      <c r="AT60" s="0"/>
+      <c r="AU60" s="0"/>
+      <c r="AV60" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="AW60" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX60" s="0"/>
+      <c r="AY60" s="0"/>
     </row>
     <row r="61" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="A61" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="C61" s="0"/>
+      <c r="D61" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="E61" s="0"/>
+      <c r="F61" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G61" s="0"/>
+      <c r="H61" s="0"/>
+      <c r="I61" s="0"/>
+      <c r="J61" s="0"/>
+      <c r="K61" s="0"/>
+      <c r="L61" s="0"/>
+      <c r="M61" s="0"/>
+      <c r="N61" s="0"/>
+      <c r="O61" s="0"/>
+      <c r="P61" s="0"/>
+      <c r="Q61" s="0"/>
+      <c r="R61" s="0"/>
+      <c r="S61" s="0"/>
+      <c r="T61" s="0"/>
+      <c r="U61" s="0"/>
+      <c r="V61" s="0"/>
+      <c r="W61" s="0"/>
+      <c r="X61" s="0"/>
+      <c r="Y61" s="0"/>
+      <c r="Z61" s="0"/>
+      <c r="AA61" s="0"/>
+      <c r="AB61" s="0"/>
+      <c r="AC61" s="0"/>
+      <c r="AD61" s="0"/>
+      <c r="AE61" s="0"/>
+      <c r="AF61" s="0"/>
+      <c r="AG61" s="0"/>
+      <c r="AH61" s="0"/>
+      <c r="AI61" s="0"/>
+      <c r="AJ61" s="0"/>
+      <c r="AK61" s="0"/>
+      <c r="AL61" s="0"/>
+      <c r="AM61" s="0"/>
+      <c r="AN61" s="0"/>
+      <c r="AO61" s="0"/>
+      <c r="AP61" s="0"/>
+      <c r="AQ61" s="0"/>
+      <c r="AR61" s="0"/>
+      <c r="AS61" s="0"/>
+      <c r="AT61" s="0"/>
+      <c r="AU61" s="0"/>
+      <c r="AV61" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="AW61" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX61" s="0"/>
+      <c r="AY61" s="0"/>
     </row>
     <row r="62" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AX62" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="AS64" s="5"/>
-      <c r="AX64" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4"/>
-    </row>
-    <row r="67" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4"/>
-    </row>
-    <row r="68" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4"/>
-    </row>
+      <c r="A62" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="C62" s="0"/>
+      <c r="D62" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="E62" s="0"/>
+      <c r="F62" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G62" s="0"/>
+      <c r="H62" s="0"/>
+      <c r="I62" s="0"/>
+      <c r="J62" s="0"/>
+      <c r="K62" s="0"/>
+      <c r="L62" s="0"/>
+      <c r="M62" s="0"/>
+      <c r="N62" s="0"/>
+      <c r="O62" s="0"/>
+      <c r="P62" s="0"/>
+      <c r="Q62" s="0"/>
+      <c r="R62" s="0"/>
+      <c r="S62" s="0"/>
+      <c r="T62" s="0"/>
+      <c r="U62" s="0"/>
+      <c r="V62" s="0"/>
+      <c r="W62" s="0"/>
+      <c r="X62" s="0"/>
+      <c r="Y62" s="0"/>
+      <c r="Z62" s="0"/>
+      <c r="AA62" s="0"/>
+      <c r="AB62" s="0"/>
+      <c r="AC62" s="0"/>
+      <c r="AD62" s="0"/>
+      <c r="AE62" s="0"/>
+      <c r="AF62" s="0"/>
+      <c r="AG62" s="0"/>
+      <c r="AH62" s="0"/>
+      <c r="AI62" s="0"/>
+      <c r="AJ62" s="0"/>
+      <c r="AK62" s="0"/>
+      <c r="AL62" s="0"/>
+      <c r="AM62" s="0"/>
+      <c r="AN62" s="0"/>
+      <c r="AO62" s="0"/>
+      <c r="AP62" s="0"/>
+      <c r="AQ62" s="0"/>
+      <c r="AR62" s="0"/>
+      <c r="AS62" s="0"/>
+      <c r="AT62" s="0"/>
+      <c r="AU62" s="0"/>
+      <c r="AV62" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="AW62" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX62" s="0"/>
+      <c r="AY62" s="0"/>
+    </row>
+    <row r="63" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="C63" s="0"/>
+      <c r="D63" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="E63" s="0"/>
+      <c r="F63" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G63" s="0"/>
+      <c r="H63" s="0"/>
+      <c r="I63" s="0"/>
+      <c r="J63" s="0"/>
+      <c r="K63" s="0"/>
+      <c r="L63" s="0"/>
+      <c r="M63" s="0"/>
+      <c r="N63" s="0"/>
+      <c r="O63" s="0"/>
+      <c r="P63" s="0"/>
+      <c r="Q63" s="0"/>
+      <c r="R63" s="0"/>
+      <c r="S63" s="0"/>
+      <c r="T63" s="0"/>
+      <c r="U63" s="0"/>
+      <c r="V63" s="0"/>
+      <c r="W63" s="0"/>
+      <c r="X63" s="0"/>
+      <c r="Y63" s="0"/>
+      <c r="Z63" s="0"/>
+      <c r="AA63" s="0"/>
+      <c r="AB63" s="0"/>
+      <c r="AC63" s="0"/>
+      <c r="AD63" s="0"/>
+      <c r="AE63" s="0"/>
+      <c r="AF63" s="0"/>
+      <c r="AG63" s="0"/>
+      <c r="AH63" s="0"/>
+      <c r="AI63" s="0"/>
+      <c r="AJ63" s="0"/>
+      <c r="AK63" s="0"/>
+      <c r="AL63" s="0"/>
+      <c r="AM63" s="0"/>
+      <c r="AN63" s="0"/>
+      <c r="AO63" s="0"/>
+      <c r="AP63" s="0"/>
+      <c r="AQ63" s="0"/>
+      <c r="AR63" s="0"/>
+      <c r="AS63" s="0"/>
+      <c r="AT63" s="0"/>
+      <c r="AU63" s="0"/>
+      <c r="AV63" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="AW63" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX63" s="0"/>
+      <c r="AY63" s="0"/>
+    </row>
+    <row r="64" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="C64" s="0"/>
+      <c r="D64" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="E64" s="0"/>
+      <c r="F64" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G64" s="0"/>
+      <c r="H64" s="0"/>
+      <c r="I64" s="0"/>
+      <c r="J64" s="0"/>
+      <c r="K64" s="0"/>
+      <c r="L64" s="0"/>
+      <c r="M64" s="0"/>
+      <c r="N64" s="0"/>
+      <c r="O64" s="0"/>
+      <c r="P64" s="0"/>
+      <c r="Q64" s="0"/>
+      <c r="R64" s="0"/>
+      <c r="S64" s="0"/>
+      <c r="T64" s="0"/>
+      <c r="U64" s="0"/>
+      <c r="V64" s="0"/>
+      <c r="W64" s="0"/>
+      <c r="X64" s="0"/>
+      <c r="Y64" s="0"/>
+      <c r="Z64" s="0"/>
+      <c r="AA64" s="0"/>
+      <c r="AB64" s="0"/>
+      <c r="AC64" s="0"/>
+      <c r="AD64" s="0"/>
+      <c r="AE64" s="0"/>
+      <c r="AF64" s="0"/>
+      <c r="AG64" s="0"/>
+      <c r="AH64" s="0"/>
+      <c r="AI64" s="0"/>
+      <c r="AJ64" s="0"/>
+      <c r="AK64" s="0"/>
+      <c r="AL64" s="0"/>
+      <c r="AM64" s="0"/>
+      <c r="AN64" s="0"/>
+      <c r="AO64" s="0"/>
+      <c r="AP64" s="0"/>
+      <c r="AQ64" s="0"/>
+      <c r="AR64" s="0"/>
+      <c r="AS64" s="0"/>
+      <c r="AT64" s="0"/>
+      <c r="AU64" s="0"/>
+      <c r="AV64" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="AW64" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX64" s="0"/>
+      <c r="AY64" s="0"/>
+    </row>
+    <row r="65" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="C65" s="0"/>
+      <c r="D65" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="E65" s="0"/>
+      <c r="F65" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G65" s="0"/>
+      <c r="H65" s="0"/>
+      <c r="I65" s="0"/>
+      <c r="J65" s="0"/>
+      <c r="K65" s="0"/>
+      <c r="L65" s="0"/>
+      <c r="M65" s="0"/>
+      <c r="N65" s="0"/>
+      <c r="O65" s="0"/>
+      <c r="P65" s="0"/>
+      <c r="Q65" s="0"/>
+      <c r="R65" s="0"/>
+      <c r="S65" s="0"/>
+      <c r="T65" s="0"/>
+      <c r="U65" s="0"/>
+      <c r="V65" s="0"/>
+      <c r="W65" s="0"/>
+      <c r="X65" s="0"/>
+      <c r="Y65" s="0"/>
+      <c r="Z65" s="0"/>
+      <c r="AA65" s="0"/>
+      <c r="AB65" s="0"/>
+      <c r="AC65" s="0"/>
+      <c r="AD65" s="0"/>
+      <c r="AE65" s="0"/>
+      <c r="AF65" s="0"/>
+      <c r="AG65" s="0"/>
+      <c r="AH65" s="0"/>
+      <c r="AI65" s="0"/>
+      <c r="AJ65" s="0"/>
+      <c r="AK65" s="0"/>
+      <c r="AL65" s="0"/>
+      <c r="AM65" s="0"/>
+      <c r="AN65" s="0"/>
+      <c r="AO65" s="0"/>
+      <c r="AP65" s="0"/>
+      <c r="AQ65" s="0"/>
+      <c r="AR65" s="0"/>
+      <c r="AS65" s="0"/>
+      <c r="AT65" s="0"/>
+      <c r="AU65" s="0"/>
+      <c r="AV65" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="AW65" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX65" s="0"/>
+      <c r="AY65" s="0"/>
+    </row>
+    <row r="66" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="C66" s="0"/>
+      <c r="D66" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="E66" s="0"/>
+      <c r="F66" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G66" s="0"/>
+      <c r="H66" s="0"/>
+      <c r="I66" s="0"/>
+      <c r="J66" s="0"/>
+      <c r="K66" s="0"/>
+      <c r="L66" s="0"/>
+      <c r="M66" s="0"/>
+      <c r="N66" s="0"/>
+      <c r="O66" s="0"/>
+      <c r="P66" s="0"/>
+      <c r="Q66" s="0"/>
+      <c r="R66" s="0"/>
+      <c r="S66" s="0"/>
+      <c r="T66" s="0"/>
+      <c r="U66" s="0"/>
+      <c r="V66" s="0"/>
+      <c r="W66" s="0"/>
+      <c r="X66" s="0"/>
+      <c r="Y66" s="0"/>
+      <c r="Z66" s="0"/>
+      <c r="AA66" s="0"/>
+      <c r="AB66" s="0"/>
+      <c r="AC66" s="0"/>
+      <c r="AD66" s="0"/>
+      <c r="AE66" s="0"/>
+      <c r="AF66" s="0"/>
+      <c r="AG66" s="0"/>
+      <c r="AH66" s="0"/>
+      <c r="AI66" s="0"/>
+      <c r="AJ66" s="0"/>
+      <c r="AK66" s="0"/>
+      <c r="AL66" s="0"/>
+      <c r="AM66" s="0"/>
+      <c r="AN66" s="0"/>
+      <c r="AO66" s="0"/>
+      <c r="AP66" s="0"/>
+      <c r="AQ66" s="0"/>
+      <c r="AR66" s="0"/>
+      <c r="AS66" s="0"/>
+      <c r="AT66" s="0"/>
+      <c r="AU66" s="0"/>
+      <c r="AV66" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="AW66" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX66" s="0"/>
+      <c r="AY66" s="0"/>
+    </row>
+    <row r="67" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C67" s="0"/>
+      <c r="D67" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="E67" s="0"/>
+      <c r="F67" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G67" s="0"/>
+      <c r="H67" s="0"/>
+      <c r="I67" s="0"/>
+      <c r="J67" s="0"/>
+      <c r="K67" s="0"/>
+      <c r="L67" s="0"/>
+      <c r="M67" s="0"/>
+      <c r="N67" s="0"/>
+      <c r="O67" s="0"/>
+      <c r="P67" s="0"/>
+      <c r="Q67" s="0"/>
+      <c r="R67" s="0"/>
+      <c r="S67" s="0"/>
+      <c r="T67" s="0"/>
+      <c r="U67" s="0"/>
+      <c r="V67" s="0"/>
+      <c r="W67" s="0"/>
+      <c r="X67" s="0"/>
+      <c r="Y67" s="0"/>
+      <c r="Z67" s="0"/>
+      <c r="AA67" s="0"/>
+      <c r="AB67" s="0"/>
+      <c r="AC67" s="0"/>
+      <c r="AD67" s="0"/>
+      <c r="AE67" s="0"/>
+      <c r="AF67" s="0"/>
+      <c r="AG67" s="0"/>
+      <c r="AH67" s="0"/>
+      <c r="AI67" s="0"/>
+      <c r="AJ67" s="0"/>
+      <c r="AK67" s="0"/>
+      <c r="AL67" s="0"/>
+      <c r="AM67" s="0"/>
+      <c r="AN67" s="0"/>
+      <c r="AO67" s="0"/>
+      <c r="AP67" s="0"/>
+      <c r="AQ67" s="0"/>
+      <c r="AR67" s="0"/>
+      <c r="AS67" s="0"/>
+      <c r="AT67" s="0"/>
+      <c r="AU67" s="0"/>
+      <c r="AV67" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW67" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX67" s="0"/>
+      <c r="AY67" s="0"/>
+    </row>
+    <row r="68" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="0"/>
+      <c r="D68" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="E68" s="0"/>
+      <c r="F68" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G68" s="0"/>
+      <c r="H68" s="0"/>
+      <c r="I68" s="0"/>
+      <c r="J68" s="0"/>
+      <c r="K68" s="0"/>
+      <c r="L68" s="0"/>
+      <c r="M68" s="0"/>
+      <c r="N68" s="0"/>
+      <c r="O68" s="0"/>
+      <c r="P68" s="0"/>
+      <c r="Q68" s="0"/>
+      <c r="R68" s="0"/>
+      <c r="S68" s="0"/>
+      <c r="T68" s="0"/>
+      <c r="U68" s="0"/>
+      <c r="V68" s="0"/>
+      <c r="W68" s="0"/>
+      <c r="X68" s="0"/>
+      <c r="Y68" s="0"/>
+      <c r="Z68" s="0"/>
+      <c r="AA68" s="0"/>
+      <c r="AB68" s="0"/>
+      <c r="AC68" s="0"/>
+      <c r="AD68" s="0"/>
+      <c r="AE68" s="0"/>
+      <c r="AF68" s="0"/>
+      <c r="AG68" s="0"/>
+      <c r="AH68" s="0"/>
+      <c r="AI68" s="0"/>
+      <c r="AJ68" s="0"/>
+      <c r="AK68" s="0"/>
+      <c r="AL68" s="0"/>
+      <c r="AM68" s="0"/>
+      <c r="AN68" s="0"/>
+      <c r="AO68" s="0"/>
+      <c r="AP68" s="0"/>
+      <c r="AQ68" s="0"/>
+      <c r="AR68" s="0"/>
+      <c r="AS68" s="0"/>
+      <c r="AT68" s="0"/>
+      <c r="AU68" s="0"/>
+      <c r="AV68" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="AW68" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX68" s="0"/>
+      <c r="AY68" s="0"/>
+    </row>
+    <row r="69" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="C69" s="0"/>
+      <c r="D69" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="E69" s="0"/>
+      <c r="F69" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G69" s="0"/>
+      <c r="H69" s="0"/>
+      <c r="I69" s="0"/>
+      <c r="J69" s="0"/>
+      <c r="K69" s="0"/>
+      <c r="L69" s="0"/>
+      <c r="M69" s="0"/>
+      <c r="N69" s="0"/>
+      <c r="O69" s="0"/>
+      <c r="P69" s="0"/>
+      <c r="Q69" s="0"/>
+      <c r="R69" s="0"/>
+      <c r="S69" s="0"/>
+      <c r="T69" s="0"/>
+      <c r="U69" s="0"/>
+      <c r="V69" s="0"/>
+      <c r="W69" s="0"/>
+      <c r="X69" s="0"/>
+      <c r="Y69" s="0"/>
+      <c r="Z69" s="0"/>
+      <c r="AA69" s="0"/>
+      <c r="AB69" s="0"/>
+      <c r="AC69" s="0"/>
+      <c r="AD69" s="0"/>
+      <c r="AE69" s="0"/>
+      <c r="AF69" s="0"/>
+      <c r="AG69" s="0"/>
+      <c r="AH69" s="0"/>
+      <c r="AI69" s="0"/>
+      <c r="AJ69" s="0"/>
+      <c r="AK69" s="0"/>
+      <c r="AL69" s="0"/>
+      <c r="AM69" s="0"/>
+      <c r="AN69" s="0"/>
+      <c r="AO69" s="0"/>
+      <c r="AP69" s="0"/>
+      <c r="AQ69" s="0"/>
+      <c r="AR69" s="0"/>
+      <c r="AS69" s="0"/>
+      <c r="AT69" s="0"/>
+      <c r="AU69" s="0"/>
+      <c r="AV69" s="0"/>
+      <c r="AW69" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX69" s="0"/>
+      <c r="AY69" s="0"/>
+    </row>
+    <row r="70" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="C70" s="0"/>
+      <c r="D70" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="E70" s="0"/>
+      <c r="F70" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G70" s="0"/>
+      <c r="H70" s="0"/>
+      <c r="I70" s="0"/>
+      <c r="J70" s="0"/>
+      <c r="K70" s="0"/>
+      <c r="L70" s="0"/>
+      <c r="M70" s="0"/>
+      <c r="N70" s="0"/>
+      <c r="O70" s="0"/>
+      <c r="P70" s="0"/>
+      <c r="Q70" s="0"/>
+      <c r="R70" s="0"/>
+      <c r="S70" s="0"/>
+      <c r="T70" s="0"/>
+      <c r="U70" s="0"/>
+      <c r="V70" s="0"/>
+      <c r="W70" s="0"/>
+      <c r="X70" s="0"/>
+      <c r="Y70" s="0"/>
+      <c r="Z70" s="0"/>
+      <c r="AA70" s="0"/>
+      <c r="AB70" s="0"/>
+      <c r="AC70" s="0"/>
+      <c r="AD70" s="0"/>
+      <c r="AE70" s="0"/>
+      <c r="AF70" s="0"/>
+      <c r="AG70" s="0"/>
+      <c r="AH70" s="0"/>
+      <c r="AI70" s="0"/>
+      <c r="AJ70" s="0"/>
+      <c r="AK70" s="0"/>
+      <c r="AL70" s="0"/>
+      <c r="AM70" s="0"/>
+      <c r="AN70" s="0"/>
+      <c r="AO70" s="0"/>
+      <c r="AP70" s="0"/>
+      <c r="AQ70" s="0"/>
+      <c r="AR70" s="0"/>
+      <c r="AS70" s="0"/>
+      <c r="AT70" s="0"/>
+      <c r="AU70" s="0"/>
+      <c r="AV70" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="AW70" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX70" s="0"/>
+      <c r="AY70" s="0"/>
+    </row>
+    <row r="71" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="C71" s="0"/>
+      <c r="D71" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="E71" s="0"/>
+      <c r="F71" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G71" s="0"/>
+      <c r="H71" s="0"/>
+      <c r="I71" s="0"/>
+      <c r="J71" s="0"/>
+      <c r="K71" s="0"/>
+      <c r="L71" s="0"/>
+      <c r="M71" s="0"/>
+      <c r="N71" s="0"/>
+      <c r="O71" s="0"/>
+      <c r="P71" s="0"/>
+      <c r="Q71" s="0"/>
+      <c r="R71" s="0"/>
+      <c r="S71" s="0"/>
+      <c r="T71" s="0"/>
+      <c r="U71" s="0"/>
+      <c r="V71" s="0"/>
+      <c r="W71" s="0"/>
+      <c r="X71" s="0"/>
+      <c r="Y71" s="0"/>
+      <c r="Z71" s="0"/>
+      <c r="AA71" s="0"/>
+      <c r="AB71" s="0"/>
+      <c r="AC71" s="0"/>
+      <c r="AD71" s="0"/>
+      <c r="AE71" s="0"/>
+      <c r="AF71" s="0"/>
+      <c r="AG71" s="0"/>
+      <c r="AH71" s="0"/>
+      <c r="AI71" s="0"/>
+      <c r="AJ71" s="0"/>
+      <c r="AK71" s="0"/>
+      <c r="AL71" s="0"/>
+      <c r="AM71" s="0"/>
+      <c r="AN71" s="0"/>
+      <c r="AO71" s="0"/>
+      <c r="AP71" s="0"/>
+      <c r="AQ71" s="0"/>
+      <c r="AR71" s="0"/>
+      <c r="AS71" s="0"/>
+      <c r="AT71" s="0"/>
+      <c r="AU71" s="0"/>
+      <c r="AV71" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="AW71" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX71" s="0"/>
+      <c r="AY71" s="0"/>
+    </row>
+    <row r="72" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="C72" s="0"/>
+      <c r="D72" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="E72" s="0"/>
+      <c r="F72" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G72" s="0"/>
+      <c r="H72" s="0"/>
+      <c r="I72" s="0"/>
+      <c r="J72" s="0"/>
+      <c r="K72" s="0"/>
+      <c r="L72" s="0"/>
+      <c r="M72" s="0"/>
+      <c r="N72" s="0"/>
+      <c r="O72" s="0"/>
+      <c r="P72" s="0"/>
+      <c r="Q72" s="0"/>
+      <c r="R72" s="0"/>
+      <c r="S72" s="0"/>
+      <c r="T72" s="0"/>
+      <c r="U72" s="0"/>
+      <c r="V72" s="0"/>
+      <c r="W72" s="0"/>
+      <c r="X72" s="0"/>
+      <c r="Y72" s="0"/>
+      <c r="Z72" s="0"/>
+      <c r="AA72" s="0"/>
+      <c r="AB72" s="0"/>
+      <c r="AC72" s="0"/>
+      <c r="AD72" s="0"/>
+      <c r="AE72" s="0"/>
+      <c r="AF72" s="0"/>
+      <c r="AG72" s="0"/>
+      <c r="AH72" s="0"/>
+      <c r="AI72" s="0"/>
+      <c r="AJ72" s="0"/>
+      <c r="AK72" s="0"/>
+      <c r="AL72" s="0"/>
+      <c r="AM72" s="0"/>
+      <c r="AN72" s="0"/>
+      <c r="AO72" s="0"/>
+      <c r="AP72" s="0"/>
+      <c r="AQ72" s="0"/>
+      <c r="AR72" s="0"/>
+      <c r="AS72" s="0"/>
+      <c r="AT72" s="0"/>
+      <c r="AU72" s="0"/>
+      <c r="AV72" s="0"/>
+      <c r="AW72" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX72" s="0"/>
+      <c r="AY72" s="0"/>
+    </row>
+    <row r="73" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="C73" s="0"/>
+      <c r="D73" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="E73" s="0"/>
+      <c r="F73" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G73" s="0"/>
+      <c r="H73" s="0"/>
+      <c r="I73" s="0"/>
+      <c r="J73" s="0"/>
+      <c r="K73" s="0"/>
+      <c r="L73" s="0"/>
+      <c r="M73" s="0"/>
+      <c r="N73" s="0"/>
+      <c r="O73" s="0"/>
+      <c r="P73" s="0"/>
+      <c r="Q73" s="0"/>
+      <c r="R73" s="0"/>
+      <c r="S73" s="0"/>
+      <c r="T73" s="0"/>
+      <c r="U73" s="0"/>
+      <c r="V73" s="0"/>
+      <c r="W73" s="0"/>
+      <c r="X73" s="0"/>
+      <c r="Y73" s="0"/>
+      <c r="Z73" s="0"/>
+      <c r="AA73" s="0"/>
+      <c r="AB73" s="0"/>
+      <c r="AC73" s="0"/>
+      <c r="AD73" s="0"/>
+      <c r="AE73" s="0"/>
+      <c r="AF73" s="0"/>
+      <c r="AG73" s="0"/>
+      <c r="AH73" s="0"/>
+      <c r="AI73" s="0"/>
+      <c r="AJ73" s="0"/>
+      <c r="AK73" s="0"/>
+      <c r="AL73" s="0"/>
+      <c r="AM73" s="0"/>
+      <c r="AN73" s="0"/>
+      <c r="AO73" s="0"/>
+      <c r="AP73" s="0"/>
+      <c r="AQ73" s="0"/>
+      <c r="AR73" s="0"/>
+      <c r="AS73" s="0"/>
+      <c r="AT73" s="0"/>
+      <c r="AU73" s="0"/>
+      <c r="AV73" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="AW73" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX73" s="0"/>
+      <c r="AY73" s="0"/>
+    </row>
+    <row r="74" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C74" s="0"/>
+      <c r="D74" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="E74" s="0"/>
+      <c r="F74" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G74" s="0"/>
+      <c r="H74" s="0"/>
+      <c r="I74" s="0"/>
+      <c r="J74" s="0"/>
+      <c r="K74" s="0"/>
+      <c r="L74" s="0"/>
+      <c r="M74" s="0"/>
+      <c r="N74" s="0"/>
+      <c r="O74" s="0"/>
+      <c r="P74" s="0"/>
+      <c r="Q74" s="0"/>
+      <c r="R74" s="0"/>
+      <c r="S74" s="0"/>
+      <c r="T74" s="0"/>
+      <c r="U74" s="0"/>
+      <c r="V74" s="0"/>
+      <c r="W74" s="0"/>
+      <c r="X74" s="0"/>
+      <c r="Y74" s="0"/>
+      <c r="Z74" s="0"/>
+      <c r="AA74" s="0"/>
+      <c r="AB74" s="0"/>
+      <c r="AC74" s="0"/>
+      <c r="AD74" s="0"/>
+      <c r="AE74" s="0"/>
+      <c r="AF74" s="0"/>
+      <c r="AG74" s="0"/>
+      <c r="AH74" s="0"/>
+      <c r="AI74" s="0"/>
+      <c r="AJ74" s="0"/>
+      <c r="AK74" s="0"/>
+      <c r="AL74" s="0"/>
+      <c r="AM74" s="0"/>
+      <c r="AN74" s="0"/>
+      <c r="AO74" s="0"/>
+      <c r="AP74" s="0"/>
+      <c r="AQ74" s="0"/>
+      <c r="AR74" s="0"/>
+      <c r="AS74" s="0"/>
+      <c r="AT74" s="0"/>
+      <c r="AU74" s="0"/>
+      <c r="AV74" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="AW74" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX74" s="0"/>
+      <c r="AY74" s="0"/>
+    </row>
+    <row r="75" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="C75" s="0"/>
+      <c r="D75" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="E75" s="0"/>
+      <c r="F75" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G75" s="0"/>
+      <c r="H75" s="0"/>
+      <c r="I75" s="0"/>
+      <c r="J75" s="0"/>
+      <c r="K75" s="0"/>
+      <c r="L75" s="0"/>
+      <c r="M75" s="0"/>
+      <c r="N75" s="0"/>
+      <c r="O75" s="0"/>
+      <c r="P75" s="0"/>
+      <c r="Q75" s="0"/>
+      <c r="R75" s="0"/>
+      <c r="S75" s="0"/>
+      <c r="T75" s="0"/>
+      <c r="U75" s="0"/>
+      <c r="V75" s="0"/>
+      <c r="W75" s="0"/>
+      <c r="X75" s="0"/>
+      <c r="Y75" s="0"/>
+      <c r="Z75" s="0"/>
+      <c r="AA75" s="0"/>
+      <c r="AB75" s="0"/>
+      <c r="AC75" s="0"/>
+      <c r="AD75" s="0"/>
+      <c r="AE75" s="0"/>
+      <c r="AF75" s="0"/>
+      <c r="AG75" s="0"/>
+      <c r="AH75" s="0"/>
+      <c r="AI75" s="0"/>
+      <c r="AJ75" s="0"/>
+      <c r="AK75" s="0"/>
+      <c r="AL75" s="0"/>
+      <c r="AM75" s="0"/>
+      <c r="AN75" s="0"/>
+      <c r="AO75" s="0"/>
+      <c r="AP75" s="0"/>
+      <c r="AQ75" s="0"/>
+      <c r="AR75" s="0"/>
+      <c r="AS75" s="0"/>
+      <c r="AT75" s="0"/>
+      <c r="AU75" s="0"/>
+      <c r="AV75" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="AW75" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX75" s="0"/>
+      <c r="AY75" s="0"/>
+    </row>
+    <row r="76" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="C77" s="0"/>
+      <c r="D77" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="E77" s="0"/>
+      <c r="F77" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G77" s="0"/>
+      <c r="H77" s="0"/>
+      <c r="I77" s="0"/>
+      <c r="J77" s="0"/>
+      <c r="K77" s="0"/>
+      <c r="L77" s="0"/>
+      <c r="M77" s="0"/>
+      <c r="N77" s="0"/>
+      <c r="O77" s="0"/>
+      <c r="P77" s="0"/>
+      <c r="Q77" s="0"/>
+      <c r="R77" s="0"/>
+      <c r="S77" s="0"/>
+      <c r="T77" s="0"/>
+      <c r="U77" s="0"/>
+      <c r="V77" s="0"/>
+      <c r="W77" s="0"/>
+      <c r="X77" s="0"/>
+      <c r="Y77" s="0"/>
+      <c r="Z77" s="0"/>
+      <c r="AA77" s="0"/>
+      <c r="AB77" s="0"/>
+      <c r="AC77" s="0"/>
+      <c r="AD77" s="0"/>
+      <c r="AE77" s="0"/>
+      <c r="AF77" s="0"/>
+      <c r="AG77" s="0"/>
+      <c r="AH77" s="0"/>
+      <c r="AI77" s="0"/>
+      <c r="AJ77" s="0"/>
+      <c r="AK77" s="0"/>
+      <c r="AL77" s="0"/>
+      <c r="AM77" s="0"/>
+      <c r="AN77" s="0"/>
+      <c r="AO77" s="0"/>
+      <c r="AP77" s="0"/>
+      <c r="AQ77" s="0"/>
+      <c r="AR77" s="0"/>
+      <c r="AS77" s="0"/>
+      <c r="AT77" s="0"/>
+      <c r="AU77" s="0"/>
+      <c r="AV77" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="AW77" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX77" s="0"/>
+      <c r="AY77" s="0"/>
+    </row>
+    <row r="78" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C78" s="0"/>
+      <c r="D78" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="E78" s="0"/>
+      <c r="F78" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G78" s="0"/>
+      <c r="H78" s="0"/>
+      <c r="I78" s="0"/>
+      <c r="J78" s="0"/>
+      <c r="K78" s="0"/>
+      <c r="L78" s="0"/>
+      <c r="M78" s="0"/>
+      <c r="N78" s="0"/>
+      <c r="O78" s="0"/>
+      <c r="P78" s="0"/>
+      <c r="Q78" s="0"/>
+      <c r="R78" s="0"/>
+      <c r="S78" s="0"/>
+      <c r="T78" s="0"/>
+      <c r="U78" s="0"/>
+      <c r="V78" s="0"/>
+      <c r="W78" s="0"/>
+      <c r="X78" s="0"/>
+      <c r="Y78" s="0"/>
+      <c r="Z78" s="0"/>
+      <c r="AA78" s="0"/>
+      <c r="AB78" s="0"/>
+      <c r="AC78" s="0"/>
+      <c r="AD78" s="0"/>
+      <c r="AE78" s="0"/>
+      <c r="AF78" s="0"/>
+      <c r="AG78" s="0"/>
+      <c r="AH78" s="0"/>
+      <c r="AI78" s="0"/>
+      <c r="AJ78" s="0"/>
+      <c r="AK78" s="0"/>
+      <c r="AL78" s="0"/>
+      <c r="AM78" s="0"/>
+      <c r="AN78" s="0"/>
+      <c r="AO78" s="0"/>
+      <c r="AP78" s="0"/>
+      <c r="AQ78" s="0"/>
+      <c r="AR78" s="0"/>
+      <c r="AS78" s="0"/>
+      <c r="AT78" s="0"/>
+      <c r="AU78" s="0"/>
+      <c r="AV78" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="AW78" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX78" s="0"/>
+      <c r="AY78" s="0"/>
+    </row>
+    <row r="79" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="C79" s="0"/>
+      <c r="D79" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="E79" s="0"/>
+      <c r="F79" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G79" s="0"/>
+      <c r="H79" s="0"/>
+      <c r="I79" s="0"/>
+      <c r="J79" s="0"/>
+      <c r="K79" s="0"/>
+      <c r="L79" s="0"/>
+      <c r="M79" s="0"/>
+      <c r="N79" s="0"/>
+      <c r="O79" s="0"/>
+      <c r="P79" s="0"/>
+      <c r="Q79" s="0"/>
+      <c r="R79" s="0"/>
+      <c r="S79" s="0"/>
+      <c r="T79" s="0"/>
+      <c r="U79" s="0"/>
+      <c r="V79" s="0"/>
+      <c r="W79" s="0"/>
+      <c r="X79" s="0"/>
+      <c r="Y79" s="0"/>
+      <c r="Z79" s="0"/>
+      <c r="AA79" s="0"/>
+      <c r="AB79" s="0"/>
+      <c r="AC79" s="0"/>
+      <c r="AD79" s="0"/>
+      <c r="AE79" s="0"/>
+      <c r="AF79" s="0"/>
+      <c r="AG79" s="0"/>
+      <c r="AH79" s="0"/>
+      <c r="AI79" s="0"/>
+      <c r="AJ79" s="0"/>
+      <c r="AK79" s="0"/>
+      <c r="AL79" s="0"/>
+      <c r="AM79" s="0"/>
+      <c r="AN79" s="0"/>
+      <c r="AO79" s="0"/>
+      <c r="AP79" s="0"/>
+      <c r="AQ79" s="0"/>
+      <c r="AR79" s="0"/>
+      <c r="AS79" s="0"/>
+      <c r="AT79" s="0"/>
+      <c r="AU79" s="0"/>
+      <c r="AV79" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="AW79" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX79" s="0"/>
+      <c r="AY79" s="0"/>
+    </row>
+    <row r="80" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="C80" s="0"/>
+      <c r="D80" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="E80" s="0"/>
+      <c r="F80" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G80" s="0"/>
+      <c r="H80" s="0"/>
+      <c r="I80" s="0"/>
+      <c r="J80" s="0"/>
+      <c r="K80" s="0"/>
+      <c r="L80" s="0"/>
+      <c r="M80" s="0"/>
+      <c r="N80" s="0"/>
+      <c r="O80" s="0"/>
+      <c r="P80" s="0"/>
+      <c r="Q80" s="0"/>
+      <c r="R80" s="0"/>
+      <c r="S80" s="0"/>
+      <c r="T80" s="0"/>
+      <c r="U80" s="0"/>
+      <c r="V80" s="0"/>
+      <c r="W80" s="0"/>
+      <c r="X80" s="0"/>
+      <c r="Y80" s="0"/>
+      <c r="Z80" s="0"/>
+      <c r="AA80" s="0"/>
+      <c r="AB80" s="0"/>
+      <c r="AC80" s="0"/>
+      <c r="AD80" s="0"/>
+      <c r="AE80" s="0"/>
+      <c r="AF80" s="0"/>
+      <c r="AG80" s="0"/>
+      <c r="AH80" s="0"/>
+      <c r="AI80" s="0"/>
+      <c r="AJ80" s="0"/>
+      <c r="AK80" s="0"/>
+      <c r="AL80" s="0"/>
+      <c r="AM80" s="0"/>
+      <c r="AN80" s="0"/>
+      <c r="AO80" s="0"/>
+      <c r="AP80" s="0"/>
+      <c r="AQ80" s="0"/>
+      <c r="AR80" s="0"/>
+      <c r="AS80" s="0"/>
+      <c r="AT80" s="0"/>
+      <c r="AU80" s="0"/>
+      <c r="AV80" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="AW80" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX80" s="0"/>
+      <c r="AY80" s="0"/>
+    </row>
+    <row r="81" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="C81" s="0"/>
+      <c r="D81" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="E81" s="0"/>
+      <c r="F81" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G81" s="0"/>
+      <c r="H81" s="0"/>
+      <c r="I81" s="0"/>
+      <c r="J81" s="0"/>
+      <c r="K81" s="0"/>
+      <c r="L81" s="0"/>
+      <c r="M81" s="0"/>
+      <c r="N81" s="0"/>
+      <c r="O81" s="0"/>
+      <c r="P81" s="0"/>
+      <c r="Q81" s="0"/>
+      <c r="R81" s="0"/>
+      <c r="S81" s="0"/>
+      <c r="T81" s="0"/>
+      <c r="U81" s="0"/>
+      <c r="V81" s="0"/>
+      <c r="W81" s="0"/>
+      <c r="X81" s="0"/>
+      <c r="Y81" s="0"/>
+      <c r="Z81" s="0"/>
+      <c r="AA81" s="0"/>
+      <c r="AB81" s="0"/>
+      <c r="AC81" s="0"/>
+      <c r="AD81" s="0"/>
+      <c r="AE81" s="0"/>
+      <c r="AF81" s="0"/>
+      <c r="AG81" s="0"/>
+      <c r="AH81" s="0"/>
+      <c r="AI81" s="0"/>
+      <c r="AJ81" s="0"/>
+      <c r="AK81" s="0"/>
+      <c r="AL81" s="0"/>
+      <c r="AM81" s="0"/>
+      <c r="AN81" s="0"/>
+      <c r="AO81" s="0"/>
+      <c r="AP81" s="0"/>
+      <c r="AQ81" s="0"/>
+      <c r="AR81" s="0"/>
+      <c r="AS81" s="0"/>
+      <c r="AT81" s="0"/>
+      <c r="AU81" s="0"/>
+      <c r="AV81" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="AW81" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX81" s="0"/>
+      <c r="AY81" s="0"/>
+    </row>
+    <row r="82" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="C82" s="0"/>
+      <c r="D82" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="E82" s="0"/>
+      <c r="F82" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G82" s="0"/>
+      <c r="H82" s="0"/>
+      <c r="I82" s="0"/>
+      <c r="J82" s="0"/>
+      <c r="K82" s="0"/>
+      <c r="L82" s="0"/>
+      <c r="M82" s="0"/>
+      <c r="N82" s="0"/>
+      <c r="O82" s="0"/>
+      <c r="P82" s="0"/>
+      <c r="Q82" s="0"/>
+      <c r="R82" s="0"/>
+      <c r="S82" s="0"/>
+      <c r="T82" s="0"/>
+      <c r="U82" s="0"/>
+      <c r="V82" s="0"/>
+      <c r="W82" s="0"/>
+      <c r="X82" s="0"/>
+      <c r="Y82" s="0"/>
+      <c r="Z82" s="0"/>
+      <c r="AA82" s="0"/>
+      <c r="AB82" s="0"/>
+      <c r="AC82" s="0"/>
+      <c r="AD82" s="0"/>
+      <c r="AE82" s="0"/>
+      <c r="AF82" s="0"/>
+      <c r="AG82" s="0"/>
+      <c r="AH82" s="0"/>
+      <c r="AI82" s="0"/>
+      <c r="AJ82" s="0"/>
+      <c r="AK82" s="0"/>
+      <c r="AL82" s="0"/>
+      <c r="AM82" s="0"/>
+      <c r="AN82" s="0"/>
+      <c r="AO82" s="0"/>
+      <c r="AP82" s="0"/>
+      <c r="AQ82" s="0"/>
+      <c r="AR82" s="0"/>
+      <c r="AS82" s="0"/>
+      <c r="AT82" s="0"/>
+      <c r="AU82" s="0"/>
+      <c r="AV82" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="AW82" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX82" s="0"/>
+      <c r="AY82" s="0"/>
+    </row>
+    <row r="83" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="C83" s="0"/>
+      <c r="D83" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="E83" s="0"/>
+      <c r="F83" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G83" s="0"/>
+      <c r="H83" s="0"/>
+      <c r="I83" s="0"/>
+      <c r="J83" s="0"/>
+      <c r="K83" s="0"/>
+      <c r="L83" s="0"/>
+      <c r="M83" s="0"/>
+      <c r="N83" s="0"/>
+      <c r="O83" s="0"/>
+      <c r="P83" s="0"/>
+      <c r="Q83" s="0"/>
+      <c r="R83" s="0"/>
+      <c r="S83" s="0"/>
+      <c r="T83" s="0"/>
+      <c r="U83" s="0"/>
+      <c r="V83" s="0"/>
+      <c r="W83" s="0"/>
+      <c r="X83" s="0"/>
+      <c r="Y83" s="0"/>
+      <c r="Z83" s="0"/>
+      <c r="AA83" s="0"/>
+      <c r="AB83" s="0"/>
+      <c r="AC83" s="0"/>
+      <c r="AD83" s="0"/>
+      <c r="AE83" s="0"/>
+      <c r="AF83" s="0"/>
+      <c r="AG83" s="0"/>
+      <c r="AH83" s="0"/>
+      <c r="AI83" s="0"/>
+      <c r="AJ83" s="0"/>
+      <c r="AK83" s="0"/>
+      <c r="AL83" s="0"/>
+      <c r="AM83" s="0"/>
+      <c r="AN83" s="0"/>
+      <c r="AO83" s="0"/>
+      <c r="AP83" s="0"/>
+      <c r="AQ83" s="0"/>
+      <c r="AR83" s="0"/>
+      <c r="AS83" s="0"/>
+      <c r="AT83" s="0"/>
+      <c r="AU83" s="0"/>
+      <c r="AV83" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="AW83" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX83" s="0"/>
+      <c r="AY83" s="0"/>
+    </row>
+    <row r="84" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="C84" s="0"/>
+      <c r="D84" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="E84" s="0"/>
+      <c r="F84" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G84" s="0"/>
+      <c r="H84" s="0"/>
+      <c r="I84" s="0"/>
+      <c r="J84" s="0"/>
+      <c r="K84" s="0"/>
+      <c r="L84" s="0"/>
+      <c r="M84" s="0"/>
+      <c r="N84" s="0"/>
+      <c r="O84" s="0"/>
+      <c r="P84" s="0"/>
+      <c r="Q84" s="0"/>
+      <c r="R84" s="0"/>
+      <c r="S84" s="0"/>
+      <c r="T84" s="0"/>
+      <c r="U84" s="0"/>
+      <c r="V84" s="0"/>
+      <c r="W84" s="0"/>
+      <c r="X84" s="0"/>
+      <c r="Y84" s="0"/>
+      <c r="Z84" s="0"/>
+      <c r="AA84" s="0"/>
+      <c r="AB84" s="0"/>
+      <c r="AC84" s="0"/>
+      <c r="AD84" s="0"/>
+      <c r="AE84" s="0"/>
+      <c r="AF84" s="0"/>
+      <c r="AG84" s="0"/>
+      <c r="AH84" s="0"/>
+      <c r="AI84" s="0"/>
+      <c r="AJ84" s="0"/>
+      <c r="AK84" s="0"/>
+      <c r="AL84" s="0"/>
+      <c r="AM84" s="0"/>
+      <c r="AN84" s="0"/>
+      <c r="AO84" s="0"/>
+      <c r="AP84" s="0"/>
+      <c r="AQ84" s="0"/>
+      <c r="AR84" s="0"/>
+      <c r="AS84" s="0"/>
+      <c r="AT84" s="0"/>
+      <c r="AU84" s="0"/>
+      <c r="AV84" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="AW84" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX84" s="0"/>
+      <c r="AY84" s="0"/>
+    </row>
+    <row r="85" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="C86" s="0"/>
+      <c r="D86" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="E86" s="0"/>
+      <c r="F86" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G86" s="0"/>
+      <c r="H86" s="0"/>
+      <c r="I86" s="0"/>
+      <c r="J86" s="0"/>
+      <c r="K86" s="0"/>
+      <c r="L86" s="0"/>
+      <c r="M86" s="0"/>
+      <c r="N86" s="0"/>
+      <c r="O86" s="0"/>
+      <c r="P86" s="0"/>
+      <c r="Q86" s="0"/>
+      <c r="R86" s="0"/>
+      <c r="S86" s="0"/>
+      <c r="T86" s="0"/>
+      <c r="U86" s="0"/>
+      <c r="V86" s="0"/>
+      <c r="W86" s="0"/>
+      <c r="X86" s="0"/>
+      <c r="Y86" s="0"/>
+      <c r="Z86" s="0"/>
+      <c r="AA86" s="0"/>
+      <c r="AB86" s="0"/>
+      <c r="AC86" s="0"/>
+      <c r="AD86" s="0"/>
+      <c r="AE86" s="0"/>
+      <c r="AF86" s="0"/>
+      <c r="AG86" s="0"/>
+      <c r="AH86" s="0"/>
+      <c r="AI86" s="0"/>
+      <c r="AJ86" s="0"/>
+      <c r="AK86" s="0"/>
+      <c r="AL86" s="0"/>
+      <c r="AM86" s="0"/>
+      <c r="AN86" s="0"/>
+      <c r="AO86" s="0"/>
+      <c r="AP86" s="0"/>
+      <c r="AQ86" s="0"/>
+      <c r="AR86" s="0"/>
+      <c r="AS86" s="0"/>
+      <c r="AT86" s="0"/>
+      <c r="AU86" s="0"/>
+      <c r="AV86" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="AW86" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX86" s="0"/>
+      <c r="AY86" s="0"/>
+    </row>
+    <row r="87" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="C87" s="0"/>
+      <c r="D87" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="E87" s="0"/>
+      <c r="F87" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G87" s="0"/>
+      <c r="H87" s="0"/>
+      <c r="I87" s="0"/>
+      <c r="J87" s="0"/>
+      <c r="K87" s="0"/>
+      <c r="L87" s="0"/>
+      <c r="M87" s="0"/>
+      <c r="N87" s="0"/>
+      <c r="O87" s="0"/>
+      <c r="P87" s="0"/>
+      <c r="Q87" s="0"/>
+      <c r="R87" s="0"/>
+      <c r="S87" s="0"/>
+      <c r="T87" s="0"/>
+      <c r="U87" s="0"/>
+      <c r="V87" s="0"/>
+      <c r="W87" s="0"/>
+      <c r="X87" s="0"/>
+      <c r="Y87" s="0"/>
+      <c r="Z87" s="0"/>
+      <c r="AA87" s="0"/>
+      <c r="AB87" s="0"/>
+      <c r="AC87" s="0"/>
+      <c r="AD87" s="0"/>
+      <c r="AE87" s="0"/>
+      <c r="AF87" s="0"/>
+      <c r="AG87" s="0"/>
+      <c r="AH87" s="0"/>
+      <c r="AI87" s="0"/>
+      <c r="AJ87" s="0"/>
+      <c r="AK87" s="0"/>
+      <c r="AL87" s="0"/>
+      <c r="AM87" s="0"/>
+      <c r="AN87" s="0"/>
+      <c r="AO87" s="0"/>
+      <c r="AP87" s="0"/>
+      <c r="AQ87" s="0"/>
+      <c r="AR87" s="0"/>
+      <c r="AS87" s="0"/>
+      <c r="AT87" s="0"/>
+      <c r="AU87" s="0"/>
+      <c r="AV87" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="AW87" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX87" s="0"/>
+      <c r="AY87" s="0"/>
+    </row>
+    <row r="88" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="C88" s="0"/>
+      <c r="D88" s="0" t="s">
+        <v>305</v>
+      </c>
+      <c r="E88" s="0"/>
+      <c r="F88" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G88" s="0"/>
+      <c r="H88" s="0"/>
+      <c r="I88" s="0"/>
+      <c r="J88" s="0"/>
+      <c r="K88" s="0"/>
+      <c r="L88" s="0"/>
+      <c r="M88" s="0"/>
+      <c r="N88" s="0"/>
+      <c r="O88" s="0"/>
+      <c r="P88" s="0"/>
+      <c r="Q88" s="0"/>
+      <c r="R88" s="0"/>
+      <c r="S88" s="0"/>
+      <c r="T88" s="0"/>
+      <c r="U88" s="0"/>
+      <c r="V88" s="0"/>
+      <c r="W88" s="0"/>
+      <c r="X88" s="0"/>
+      <c r="Y88" s="0"/>
+      <c r="Z88" s="0"/>
+      <c r="AA88" s="0"/>
+      <c r="AB88" s="0"/>
+      <c r="AC88" s="0"/>
+      <c r="AD88" s="0"/>
+      <c r="AE88" s="0"/>
+      <c r="AF88" s="0"/>
+      <c r="AG88" s="0"/>
+      <c r="AH88" s="0"/>
+      <c r="AI88" s="0"/>
+      <c r="AJ88" s="0"/>
+      <c r="AK88" s="0"/>
+      <c r="AL88" s="0"/>
+      <c r="AM88" s="0"/>
+      <c r="AN88" s="0"/>
+      <c r="AO88" s="0"/>
+      <c r="AP88" s="0"/>
+      <c r="AQ88" s="0"/>
+      <c r="AR88" s="0"/>
+      <c r="AS88" s="0"/>
+      <c r="AT88" s="0"/>
+      <c r="AU88" s="0"/>
+      <c r="AV88" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="AW88" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX88" s="0"/>
+      <c r="AY88" s="0"/>
+    </row>
+    <row r="89" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="C89" s="0"/>
+      <c r="D89" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="E89" s="0"/>
+      <c r="F89" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G89" s="0"/>
+      <c r="H89" s="0"/>
+      <c r="I89" s="0"/>
+      <c r="J89" s="0"/>
+      <c r="K89" s="0"/>
+      <c r="L89" s="0"/>
+      <c r="M89" s="0"/>
+      <c r="N89" s="0"/>
+      <c r="O89" s="0"/>
+      <c r="P89" s="0"/>
+      <c r="Q89" s="0"/>
+      <c r="R89" s="0"/>
+      <c r="S89" s="0"/>
+      <c r="T89" s="0"/>
+      <c r="U89" s="0"/>
+      <c r="V89" s="0"/>
+      <c r="W89" s="0"/>
+      <c r="X89" s="0"/>
+      <c r="Y89" s="0"/>
+      <c r="Z89" s="0"/>
+      <c r="AA89" s="0"/>
+      <c r="AB89" s="0"/>
+      <c r="AC89" s="0"/>
+      <c r="AD89" s="0"/>
+      <c r="AE89" s="0"/>
+      <c r="AF89" s="0"/>
+      <c r="AG89" s="0"/>
+      <c r="AH89" s="0"/>
+      <c r="AI89" s="0"/>
+      <c r="AJ89" s="0"/>
+      <c r="AK89" s="0"/>
+      <c r="AL89" s="0"/>
+      <c r="AM89" s="0"/>
+      <c r="AN89" s="0"/>
+      <c r="AO89" s="0"/>
+      <c r="AP89" s="0"/>
+      <c r="AQ89" s="0"/>
+      <c r="AR89" s="0"/>
+      <c r="AS89" s="0"/>
+      <c r="AT89" s="0"/>
+      <c r="AU89" s="0"/>
+      <c r="AV89" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="AW89" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX89" s="0"/>
+      <c r="AY89" s="0"/>
+    </row>
+    <row r="90" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="C90" s="0"/>
+      <c r="D90" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="E90" s="0"/>
+      <c r="F90" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G90" s="0"/>
+      <c r="H90" s="0"/>
+      <c r="I90" s="0"/>
+      <c r="J90" s="0"/>
+      <c r="K90" s="0"/>
+      <c r="L90" s="0"/>
+      <c r="M90" s="0"/>
+      <c r="N90" s="0"/>
+      <c r="O90" s="0"/>
+      <c r="P90" s="0"/>
+      <c r="Q90" s="0"/>
+      <c r="R90" s="0"/>
+      <c r="S90" s="0"/>
+      <c r="T90" s="0"/>
+      <c r="U90" s="0"/>
+      <c r="V90" s="0"/>
+      <c r="W90" s="0"/>
+      <c r="X90" s="0"/>
+      <c r="Y90" s="0"/>
+      <c r="Z90" s="0"/>
+      <c r="AA90" s="0"/>
+      <c r="AB90" s="0"/>
+      <c r="AC90" s="0"/>
+      <c r="AD90" s="0"/>
+      <c r="AE90" s="0"/>
+      <c r="AF90" s="0"/>
+      <c r="AG90" s="0"/>
+      <c r="AH90" s="0"/>
+      <c r="AI90" s="0"/>
+      <c r="AJ90" s="0"/>
+      <c r="AK90" s="0"/>
+      <c r="AL90" s="0"/>
+      <c r="AM90" s="0"/>
+      <c r="AN90" s="0"/>
+      <c r="AO90" s="0"/>
+      <c r="AP90" s="0"/>
+      <c r="AQ90" s="0"/>
+      <c r="AR90" s="0"/>
+      <c r="AS90" s="0"/>
+      <c r="AT90" s="0"/>
+      <c r="AU90" s="0"/>
+      <c r="AV90" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="AW90" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX90" s="0"/>
+      <c r="AY90" s="0"/>
+    </row>
+    <row r="91" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="C91" s="0"/>
+      <c r="D91" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="E91" s="0"/>
+      <c r="F91" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G91" s="0"/>
+      <c r="H91" s="0"/>
+      <c r="I91" s="0"/>
+      <c r="J91" s="0"/>
+      <c r="K91" s="0"/>
+      <c r="L91" s="0"/>
+      <c r="M91" s="0"/>
+      <c r="N91" s="0"/>
+      <c r="O91" s="0"/>
+      <c r="P91" s="0"/>
+      <c r="Q91" s="0"/>
+      <c r="R91" s="0"/>
+      <c r="S91" s="0"/>
+      <c r="T91" s="0"/>
+      <c r="U91" s="0"/>
+      <c r="V91" s="0"/>
+      <c r="W91" s="0"/>
+      <c r="X91" s="0"/>
+      <c r="Y91" s="0"/>
+      <c r="Z91" s="0"/>
+      <c r="AA91" s="0"/>
+      <c r="AB91" s="0"/>
+      <c r="AC91" s="0"/>
+      <c r="AD91" s="0"/>
+      <c r="AE91" s="0"/>
+      <c r="AF91" s="0"/>
+      <c r="AG91" s="0"/>
+      <c r="AH91" s="0"/>
+      <c r="AI91" s="0"/>
+      <c r="AJ91" s="0"/>
+      <c r="AK91" s="0"/>
+      <c r="AL91" s="0"/>
+      <c r="AM91" s="0"/>
+      <c r="AN91" s="0"/>
+      <c r="AO91" s="0"/>
+      <c r="AP91" s="0"/>
+      <c r="AQ91" s="0"/>
+      <c r="AR91" s="0"/>
+      <c r="AS91" s="0"/>
+      <c r="AT91" s="0"/>
+      <c r="AU91" s="0"/>
+      <c r="AV91" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="AW91" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX91" s="0"/>
+      <c r="AY91" s="0"/>
+    </row>
+    <row r="92" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="C92" s="0"/>
+      <c r="D92" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="E92" s="0"/>
+      <c r="F92" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G92" s="0"/>
+      <c r="H92" s="0"/>
+      <c r="I92" s="0"/>
+      <c r="J92" s="0"/>
+      <c r="K92" s="0"/>
+      <c r="L92" s="0"/>
+      <c r="M92" s="0"/>
+      <c r="N92" s="0"/>
+      <c r="O92" s="0"/>
+      <c r="P92" s="0"/>
+      <c r="Q92" s="0"/>
+      <c r="R92" s="0"/>
+      <c r="S92" s="0"/>
+      <c r="T92" s="0"/>
+      <c r="U92" s="0"/>
+      <c r="V92" s="0"/>
+      <c r="W92" s="0"/>
+      <c r="X92" s="0"/>
+      <c r="Y92" s="0"/>
+      <c r="Z92" s="0"/>
+      <c r="AA92" s="0"/>
+      <c r="AB92" s="0"/>
+      <c r="AC92" s="0"/>
+      <c r="AD92" s="0"/>
+      <c r="AE92" s="0"/>
+      <c r="AF92" s="0"/>
+      <c r="AG92" s="0"/>
+      <c r="AH92" s="0"/>
+      <c r="AI92" s="0"/>
+      <c r="AJ92" s="0"/>
+      <c r="AK92" s="0"/>
+      <c r="AL92" s="0"/>
+      <c r="AM92" s="0"/>
+      <c r="AN92" s="0"/>
+      <c r="AO92" s="0"/>
+      <c r="AP92" s="0"/>
+      <c r="AQ92" s="0"/>
+      <c r="AR92" s="0"/>
+      <c r="AS92" s="0"/>
+      <c r="AT92" s="0"/>
+      <c r="AU92" s="0"/>
+      <c r="AV92" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="AW92" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX92" s="0"/>
+      <c r="AY92" s="0"/>
+    </row>
+    <row r="93" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="C93" s="0"/>
+      <c r="D93" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="E93" s="0"/>
+      <c r="F93" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G93" s="0"/>
+      <c r="H93" s="0"/>
+      <c r="I93" s="0"/>
+      <c r="J93" s="0"/>
+      <c r="K93" s="0"/>
+      <c r="L93" s="0"/>
+      <c r="M93" s="0"/>
+      <c r="N93" s="0"/>
+      <c r="O93" s="0"/>
+      <c r="P93" s="0"/>
+      <c r="Q93" s="0"/>
+      <c r="R93" s="0"/>
+      <c r="S93" s="0"/>
+      <c r="T93" s="0"/>
+      <c r="U93" s="0"/>
+      <c r="V93" s="0"/>
+      <c r="W93" s="0"/>
+      <c r="X93" s="0"/>
+      <c r="Y93" s="0"/>
+      <c r="Z93" s="0"/>
+      <c r="AA93" s="0"/>
+      <c r="AB93" s="0"/>
+      <c r="AC93" s="0"/>
+      <c r="AD93" s="0"/>
+      <c r="AE93" s="0"/>
+      <c r="AF93" s="0"/>
+      <c r="AG93" s="0"/>
+      <c r="AH93" s="0"/>
+      <c r="AI93" s="0"/>
+      <c r="AJ93" s="0"/>
+      <c r="AK93" s="0"/>
+      <c r="AL93" s="0"/>
+      <c r="AM93" s="0"/>
+      <c r="AN93" s="0"/>
+      <c r="AO93" s="0"/>
+      <c r="AP93" s="0"/>
+      <c r="AQ93" s="0"/>
+      <c r="AR93" s="0"/>
+      <c r="AS93" s="0"/>
+      <c r="AT93" s="0"/>
+      <c r="AU93" s="0"/>
+      <c r="AV93" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="AW93" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX93" s="0"/>
+      <c r="AY93" s="0"/>
+    </row>
+    <row r="94" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="C94" s="0"/>
+      <c r="D94" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="E94" s="0"/>
+      <c r="F94" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G94" s="0"/>
+      <c r="H94" s="0"/>
+      <c r="I94" s="0"/>
+      <c r="J94" s="0"/>
+      <c r="K94" s="0"/>
+      <c r="L94" s="0"/>
+      <c r="M94" s="0"/>
+      <c r="N94" s="0"/>
+      <c r="O94" s="0"/>
+      <c r="P94" s="0"/>
+      <c r="Q94" s="0"/>
+      <c r="R94" s="0"/>
+      <c r="S94" s="0"/>
+      <c r="T94" s="0"/>
+      <c r="U94" s="0"/>
+      <c r="V94" s="0"/>
+      <c r="W94" s="0"/>
+      <c r="X94" s="0"/>
+      <c r="Y94" s="0"/>
+      <c r="Z94" s="0"/>
+      <c r="AA94" s="0"/>
+      <c r="AB94" s="0"/>
+      <c r="AC94" s="0"/>
+      <c r="AD94" s="0"/>
+      <c r="AE94" s="0"/>
+      <c r="AF94" s="0"/>
+      <c r="AG94" s="0"/>
+      <c r="AH94" s="0"/>
+      <c r="AI94" s="0"/>
+      <c r="AJ94" s="0"/>
+      <c r="AK94" s="0"/>
+      <c r="AL94" s="0"/>
+      <c r="AM94" s="0"/>
+      <c r="AN94" s="0"/>
+      <c r="AO94" s="0"/>
+      <c r="AP94" s="0"/>
+      <c r="AQ94" s="0"/>
+      <c r="AR94" s="0"/>
+      <c r="AS94" s="0"/>
+      <c r="AT94" s="0"/>
+      <c r="AU94" s="0"/>
+      <c r="AV94" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="AW94" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX94" s="0"/>
+      <c r="AY94" s="0"/>
+    </row>
+    <row r="95" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="C96" s="0"/>
+      <c r="D96" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="E96" s="0"/>
+      <c r="F96" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G96" s="0"/>
+      <c r="H96" s="0"/>
+      <c r="I96" s="0"/>
+      <c r="J96" s="0"/>
+      <c r="K96" s="0"/>
+      <c r="L96" s="0"/>
+      <c r="M96" s="0"/>
+      <c r="N96" s="0"/>
+      <c r="O96" s="0"/>
+      <c r="P96" s="0"/>
+      <c r="Q96" s="0"/>
+      <c r="R96" s="0"/>
+      <c r="S96" s="0"/>
+      <c r="T96" s="0"/>
+      <c r="U96" s="0"/>
+      <c r="V96" s="0"/>
+      <c r="W96" s="0"/>
+      <c r="X96" s="0"/>
+      <c r="Y96" s="0"/>
+      <c r="Z96" s="0"/>
+      <c r="AA96" s="0"/>
+      <c r="AB96" s="0"/>
+      <c r="AC96" s="0"/>
+      <c r="AD96" s="0"/>
+      <c r="AE96" s="0"/>
+      <c r="AF96" s="0"/>
+      <c r="AG96" s="0"/>
+      <c r="AH96" s="0"/>
+      <c r="AI96" s="0"/>
+      <c r="AJ96" s="0"/>
+      <c r="AK96" s="0"/>
+      <c r="AL96" s="0"/>
+      <c r="AM96" s="0"/>
+      <c r="AN96" s="0"/>
+      <c r="AO96" s="0"/>
+      <c r="AP96" s="0"/>
+      <c r="AQ96" s="0"/>
+      <c r="AR96" s="0"/>
+      <c r="AS96" s="0"/>
+      <c r="AT96" s="0"/>
+      <c r="AU96" s="0"/>
+      <c r="AV96" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="AW96" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX96" s="0"/>
+      <c r="AY96" s="0"/>
+    </row>
+    <row r="97" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="R103" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="M108" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="AX116" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="AS117" s="5"/>
+      <c r="AX117" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="19" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1048363" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048364" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048365" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048366" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048367" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048368" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048369" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048370" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2584,7 +6782,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
@@ -2592,48 +6790,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>226</v>
+        <v>377</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>227</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>228</v>
+        <v>379</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>229</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>231</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>232</v>
+        <v>383</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>233</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>234</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2641,7 +6839,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>235</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2649,7 +6847,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2657,7 +6855,7 @@
         <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>237</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2665,7 +6863,7 @@
         <v>37</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>238</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2673,7 +6871,7 @@
         <v>38</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>239</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2681,7 +6879,7 @@
         <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>240</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2689,7 +6887,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>241</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2697,7 +6895,7 @@
         <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>242</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2705,7 +6903,7 @@
         <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>243</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2713,7 +6911,7 @@
         <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>244</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -2733,7 +6931,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
@@ -2747,25 +6945,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>396</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>397</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>398</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>248</v>
+        <v>399</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>249</v>
+        <v>400</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>250</v>
+        <v>401</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>251</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
